--- a/docs/StructureDefinition-VAERSBundle.xlsx
+++ b/docs/StructureDefinition-VAERSBundle.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.334</t>
+    <t>0.65.339</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-17T06:29:49+00:00</t>
+    <t>2024-08-18T10:15:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA file undefined (undefined) to Bundle</t>
+    <t>This StructureDefinition contains the maps for ADERS to Bundle</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -237,7 +237,7 @@
     <t>Constraint(s)</t>
   </si>
   <si>
-    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
+    <t>Mapping: VA Adverse Drug Event Reporting System (VA ADERS)</t>
   </si>
   <si>
     <t>Mapping: Clinical Data Warehouse (CDW)</t>
@@ -2330,7 +2330,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="88.6875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="67.44921875" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="43.94140625" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="28.1484375" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="24.98046875" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-VAERSBundle.xlsx
+++ b/docs/StructureDefinition-VAERSBundle.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.339</t>
+    <t>0.65.341</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-18T10:15:47+00:00</t>
+    <t>2024-08-20T15:42:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSBundle.xlsx
+++ b/docs/StructureDefinition-VAERSBundle.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.341</t>
+    <t>0.65.343</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-20T15:42:57+00:00</t>
+    <t>2024-08-24T10:06:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSBundle.xlsx
+++ b/docs/StructureDefinition-VAERSBundle.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13935" uniqueCount="636">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13927" uniqueCount="637">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.343</t>
+    <t>0.65.345</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-24T10:06:05+00:00</t>
+    <t>2024-08-26T15:27:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1012,6 +1012,9 @@
   </si>
   <si>
     <t>Immunization event information</t>
+  </si>
+  <si>
+    <t>Describes the event of a patient being administered a vaccine or a record of an immunization as reported by a patient, a clinician or another party.</t>
   </si>
   <si>
     <t>1963: reference</t>
@@ -12640,11 +12643,9 @@
         <v>317</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="N87" t="s" s="2">
-        <v>279</v>
-      </c>
+        <v>318</v>
+      </c>
+      <c r="N87" s="2"/>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
         <v>79</v>
@@ -12708,16 +12709,16 @@
         <v>79</v>
       </c>
       <c r="AK87" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AL87" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>79</v>
@@ -12728,7 +12729,7 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B88" t="s" s="2">
         <v>198</v>
@@ -12846,7 +12847,7 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B89" t="s" s="2">
         <v>202</v>
@@ -12964,7 +12965,7 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B90" t="s" s="2">
         <v>203</v>
@@ -13084,7 +13085,7 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B91" t="s" s="2">
         <v>204</v>
@@ -13206,7 +13207,7 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B92" t="s" s="2">
         <v>205</v>
@@ -13326,7 +13327,7 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B93" t="s" s="2">
         <v>211</v>
@@ -13446,7 +13447,7 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B94" t="s" s="2">
         <v>216</v>
@@ -13564,7 +13565,7 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B95" t="s" s="2">
         <v>220</v>
@@ -13682,7 +13683,7 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B96" t="s" s="2">
         <v>221</v>
@@ -13802,7 +13803,7 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B97" t="s" s="2">
         <v>222</v>
@@ -13924,7 +13925,7 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B98" t="s" s="2">
         <v>223</v>
@@ -14042,7 +14043,7 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B99" t="s" s="2">
         <v>228</v>
@@ -14162,7 +14163,7 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B100" t="s" s="2">
         <v>232</v>
@@ -14280,7 +14281,7 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B101" t="s" s="2">
         <v>235</v>
@@ -14398,7 +14399,7 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B102" t="s" s="2">
         <v>237</v>
@@ -14516,7 +14517,7 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B103" t="s" s="2">
         <v>240</v>
@@ -14634,7 +14635,7 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B104" t="s" s="2">
         <v>243</v>
@@ -14752,7 +14753,7 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B105" t="s" s="2">
         <v>247</v>
@@ -14870,7 +14871,7 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B106" t="s" s="2">
         <v>248</v>
@@ -14990,7 +14991,7 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B107" t="s" s="2">
         <v>249</v>
@@ -15112,7 +15113,7 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B108" t="s" s="2">
         <v>250</v>
@@ -15230,7 +15231,7 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B109" t="s" s="2">
         <v>253</v>
@@ -15348,7 +15349,7 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B110" t="s" s="2">
         <v>256</v>
@@ -15468,7 +15469,7 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B111" t="s" s="2">
         <v>260</v>
@@ -15588,7 +15589,7 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B112" t="s" s="2">
         <v>264</v>
@@ -15708,13 +15709,13 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B113" t="s" s="2">
         <v>178</v>
       </c>
       <c r="C113" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="D113" t="s" s="2">
         <v>79</v>
@@ -15828,7 +15829,7 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B114" t="s" s="2">
         <v>184</v>
@@ -15946,7 +15947,7 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B115" t="s" s="2">
         <v>185</v>
@@ -16066,7 +16067,7 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B116" t="s" s="2">
         <v>186</v>
@@ -16188,7 +16189,7 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B117" t="s" s="2">
         <v>187</v>
@@ -16306,7 +16307,7 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B118" t="s" s="2">
         <v>190</v>
@@ -16426,7 +16427,7 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B119" t="s" s="2">
         <v>194</v>
@@ -16452,17 +16453,15 @@
         <v>79</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="L119" t="s" s="2">
         <v>317</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="N119" t="s" s="2">
-        <v>279</v>
-      </c>
+        <v>318</v>
+      </c>
+      <c r="N119" s="2"/>
       <c r="O119" s="2"/>
       <c r="P119" t="s" s="2">
         <v>79</v>
@@ -16526,16 +16525,16 @@
         <v>79</v>
       </c>
       <c r="AK119" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AL119" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM119" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AN119" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AO119" t="s" s="2">
         <v>79</v>
@@ -16546,7 +16545,7 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B120" t="s" s="2">
         <v>198</v>
@@ -16664,7 +16663,7 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B121" t="s" s="2">
         <v>202</v>
@@ -16782,7 +16781,7 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B122" t="s" s="2">
         <v>203</v>
@@ -16902,7 +16901,7 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B123" t="s" s="2">
         <v>204</v>
@@ -17024,7 +17023,7 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B124" t="s" s="2">
         <v>205</v>
@@ -17144,7 +17143,7 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B125" t="s" s="2">
         <v>211</v>
@@ -17264,7 +17263,7 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B126" t="s" s="2">
         <v>216</v>
@@ -17382,7 +17381,7 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B127" t="s" s="2">
         <v>220</v>
@@ -17500,7 +17499,7 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B128" t="s" s="2">
         <v>221</v>
@@ -17620,7 +17619,7 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B129" t="s" s="2">
         <v>222</v>
@@ -17742,7 +17741,7 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B130" t="s" s="2">
         <v>223</v>
@@ -17860,7 +17859,7 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B131" t="s" s="2">
         <v>228</v>
@@ -17980,7 +17979,7 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B132" t="s" s="2">
         <v>232</v>
@@ -18098,7 +18097,7 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B133" t="s" s="2">
         <v>235</v>
@@ -18216,7 +18215,7 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B134" t="s" s="2">
         <v>237</v>
@@ -18334,7 +18333,7 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B135" t="s" s="2">
         <v>240</v>
@@ -18452,7 +18451,7 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B136" t="s" s="2">
         <v>243</v>
@@ -18570,7 +18569,7 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B137" t="s" s="2">
         <v>247</v>
@@ -18688,7 +18687,7 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B138" t="s" s="2">
         <v>248</v>
@@ -18808,7 +18807,7 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B139" t="s" s="2">
         <v>249</v>
@@ -18930,7 +18929,7 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B140" t="s" s="2">
         <v>250</v>
@@ -19048,7 +19047,7 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B141" t="s" s="2">
         <v>253</v>
@@ -19166,7 +19165,7 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B142" t="s" s="2">
         <v>256</v>
@@ -19286,7 +19285,7 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B143" t="s" s="2">
         <v>260</v>
@@ -19406,7 +19405,7 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B144" t="s" s="2">
         <v>264</v>
@@ -19526,13 +19525,13 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B145" t="s" s="2">
         <v>178</v>
       </c>
       <c r="C145" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="D145" t="s" s="2">
         <v>79</v>
@@ -19646,7 +19645,7 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B146" t="s" s="2">
         <v>184</v>
@@ -19764,7 +19763,7 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B147" t="s" s="2">
         <v>185</v>
@@ -19884,7 +19883,7 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B148" t="s" s="2">
         <v>186</v>
@@ -20006,7 +20005,7 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B149" t="s" s="2">
         <v>187</v>
@@ -20124,7 +20123,7 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B150" t="s" s="2">
         <v>190</v>
@@ -20244,7 +20243,7 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B151" t="s" s="2">
         <v>194</v>
@@ -20270,17 +20269,15 @@
         <v>79</v>
       </c>
       <c r="K151" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="L151" t="s" s="2">
         <v>317</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="N151" t="s" s="2">
-        <v>279</v>
-      </c>
+        <v>318</v>
+      </c>
+      <c r="N151" s="2"/>
       <c r="O151" s="2"/>
       <c r="P151" t="s" s="2">
         <v>79</v>
@@ -20344,16 +20341,16 @@
         <v>79</v>
       </c>
       <c r="AK151" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AL151" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM151" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AN151" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AO151" t="s" s="2">
         <v>79</v>
@@ -20364,7 +20361,7 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B152" t="s" s="2">
         <v>198</v>
@@ -20482,7 +20479,7 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B153" t="s" s="2">
         <v>202</v>
@@ -20600,7 +20597,7 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B154" t="s" s="2">
         <v>203</v>
@@ -20720,7 +20717,7 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B155" t="s" s="2">
         <v>204</v>
@@ -20842,7 +20839,7 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B156" t="s" s="2">
         <v>205</v>
@@ -20962,7 +20959,7 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B157" t="s" s="2">
         <v>211</v>
@@ -21082,7 +21079,7 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B158" t="s" s="2">
         <v>216</v>
@@ -21200,7 +21197,7 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B159" t="s" s="2">
         <v>220</v>
@@ -21318,7 +21315,7 @@
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B160" t="s" s="2">
         <v>221</v>
@@ -21438,7 +21435,7 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B161" t="s" s="2">
         <v>222</v>
@@ -21560,7 +21557,7 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B162" t="s" s="2">
         <v>223</v>
@@ -21678,7 +21675,7 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B163" t="s" s="2">
         <v>228</v>
@@ -21798,7 +21795,7 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B164" t="s" s="2">
         <v>232</v>
@@ -21916,7 +21913,7 @@
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B165" t="s" s="2">
         <v>235</v>
@@ -22034,7 +22031,7 @@
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B166" t="s" s="2">
         <v>237</v>
@@ -22152,7 +22149,7 @@
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B167" t="s" s="2">
         <v>240</v>
@@ -22270,7 +22267,7 @@
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B168" t="s" s="2">
         <v>243</v>
@@ -22388,7 +22385,7 @@
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B169" t="s" s="2">
         <v>247</v>
@@ -22506,7 +22503,7 @@
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B170" t="s" s="2">
         <v>248</v>
@@ -22626,7 +22623,7 @@
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B171" t="s" s="2">
         <v>249</v>
@@ -22748,7 +22745,7 @@
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B172" t="s" s="2">
         <v>250</v>
@@ -22866,7 +22863,7 @@
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B173" t="s" s="2">
         <v>253</v>
@@ -22984,7 +22981,7 @@
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B174" t="s" s="2">
         <v>256</v>
@@ -23104,7 +23101,7 @@
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B175" t="s" s="2">
         <v>260</v>
@@ -23224,7 +23221,7 @@
     </row>
     <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B176" t="s" s="2">
         <v>264</v>
@@ -23344,13 +23341,13 @@
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B177" t="s" s="2">
         <v>178</v>
       </c>
       <c r="C177" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="D177" t="s" s="2">
         <v>79</v>
@@ -23464,7 +23461,7 @@
     </row>
     <row r="178" hidden="true">
       <c r="A178" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B178" t="s" s="2">
         <v>184</v>
@@ -23582,7 +23579,7 @@
     </row>
     <row r="179" hidden="true">
       <c r="A179" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B179" t="s" s="2">
         <v>185</v>
@@ -23702,7 +23699,7 @@
     </row>
     <row r="180" hidden="true">
       <c r="A180" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B180" t="s" s="2">
         <v>186</v>
@@ -23824,7 +23821,7 @@
     </row>
     <row r="181" hidden="true">
       <c r="A181" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B181" t="s" s="2">
         <v>187</v>
@@ -23942,7 +23939,7 @@
     </row>
     <row r="182" hidden="true">
       <c r="A182" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B182" t="s" s="2">
         <v>190</v>
@@ -24062,7 +24059,7 @@
     </row>
     <row r="183" hidden="true">
       <c r="A183" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B183" t="s" s="2">
         <v>194</v>
@@ -24088,17 +24085,15 @@
         <v>79</v>
       </c>
       <c r="K183" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="L183" t="s" s="2">
         <v>317</v>
       </c>
       <c r="M183" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="N183" t="s" s="2">
-        <v>279</v>
-      </c>
+        <v>318</v>
+      </c>
+      <c r="N183" s="2"/>
       <c r="O183" s="2"/>
       <c r="P183" t="s" s="2">
         <v>79</v>
@@ -24162,16 +24157,16 @@
         <v>79</v>
       </c>
       <c r="AK183" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AL183" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM183" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AN183" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AO183" t="s" s="2">
         <v>79</v>
@@ -24182,7 +24177,7 @@
     </row>
     <row r="184" hidden="true">
       <c r="A184" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B184" t="s" s="2">
         <v>198</v>
@@ -24300,7 +24295,7 @@
     </row>
     <row r="185" hidden="true">
       <c r="A185" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B185" t="s" s="2">
         <v>202</v>
@@ -24418,7 +24413,7 @@
     </row>
     <row r="186" hidden="true">
       <c r="A186" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B186" t="s" s="2">
         <v>203</v>
@@ -24538,7 +24533,7 @@
     </row>
     <row r="187" hidden="true">
       <c r="A187" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B187" t="s" s="2">
         <v>204</v>
@@ -24660,7 +24655,7 @@
     </row>
     <row r="188" hidden="true">
       <c r="A188" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B188" t="s" s="2">
         <v>205</v>
@@ -24780,7 +24775,7 @@
     </row>
     <row r="189" hidden="true">
       <c r="A189" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B189" t="s" s="2">
         <v>211</v>
@@ -24900,7 +24895,7 @@
     </row>
     <row r="190" hidden="true">
       <c r="A190" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B190" t="s" s="2">
         <v>216</v>
@@ -25018,7 +25013,7 @@
     </row>
     <row r="191" hidden="true">
       <c r="A191" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B191" t="s" s="2">
         <v>220</v>
@@ -25136,7 +25131,7 @@
     </row>
     <row r="192" hidden="true">
       <c r="A192" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B192" t="s" s="2">
         <v>221</v>
@@ -25256,7 +25251,7 @@
     </row>
     <row r="193" hidden="true">
       <c r="A193" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B193" t="s" s="2">
         <v>222</v>
@@ -25378,7 +25373,7 @@
     </row>
     <row r="194" hidden="true">
       <c r="A194" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B194" t="s" s="2">
         <v>223</v>
@@ -25496,7 +25491,7 @@
     </row>
     <row r="195" hidden="true">
       <c r="A195" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B195" t="s" s="2">
         <v>228</v>
@@ -25616,7 +25611,7 @@
     </row>
     <row r="196" hidden="true">
       <c r="A196" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B196" t="s" s="2">
         <v>232</v>
@@ -25734,7 +25729,7 @@
     </row>
     <row r="197" hidden="true">
       <c r="A197" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B197" t="s" s="2">
         <v>235</v>
@@ -25852,7 +25847,7 @@
     </row>
     <row r="198" hidden="true">
       <c r="A198" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B198" t="s" s="2">
         <v>237</v>
@@ -25970,7 +25965,7 @@
     </row>
     <row r="199" hidden="true">
       <c r="A199" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B199" t="s" s="2">
         <v>240</v>
@@ -26088,7 +26083,7 @@
     </row>
     <row r="200" hidden="true">
       <c r="A200" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B200" t="s" s="2">
         <v>243</v>
@@ -26206,7 +26201,7 @@
     </row>
     <row r="201" hidden="true">
       <c r="A201" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B201" t="s" s="2">
         <v>247</v>
@@ -26324,7 +26319,7 @@
     </row>
     <row r="202" hidden="true">
       <c r="A202" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B202" t="s" s="2">
         <v>248</v>
@@ -26444,7 +26439,7 @@
     </row>
     <row r="203" hidden="true">
       <c r="A203" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B203" t="s" s="2">
         <v>249</v>
@@ -26566,7 +26561,7 @@
     </row>
     <row r="204" hidden="true">
       <c r="A204" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B204" t="s" s="2">
         <v>250</v>
@@ -26684,7 +26679,7 @@
     </row>
     <row r="205" hidden="true">
       <c r="A205" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B205" t="s" s="2">
         <v>253</v>
@@ -26802,7 +26797,7 @@
     </row>
     <row r="206" hidden="true">
       <c r="A206" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B206" t="s" s="2">
         <v>256</v>
@@ -26922,7 +26917,7 @@
     </row>
     <row r="207" hidden="true">
       <c r="A207" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B207" t="s" s="2">
         <v>260</v>
@@ -27042,7 +27037,7 @@
     </row>
     <row r="208" hidden="true">
       <c r="A208" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B208" t="s" s="2">
         <v>264</v>
@@ -27162,13 +27157,13 @@
     </row>
     <row r="209" hidden="true">
       <c r="A209" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B209" t="s" s="2">
         <v>178</v>
       </c>
       <c r="C209" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="D209" t="s" s="2">
         <v>79</v>
@@ -27282,7 +27277,7 @@
     </row>
     <row r="210" hidden="true">
       <c r="A210" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B210" t="s" s="2">
         <v>184</v>
@@ -27400,7 +27395,7 @@
     </row>
     <row r="211" hidden="true">
       <c r="A211" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B211" t="s" s="2">
         <v>185</v>
@@ -27520,7 +27515,7 @@
     </row>
     <row r="212" hidden="true">
       <c r="A212" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B212" t="s" s="2">
         <v>186</v>
@@ -27642,7 +27637,7 @@
     </row>
     <row r="213" hidden="true">
       <c r="A213" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B213" t="s" s="2">
         <v>187</v>
@@ -27760,7 +27755,7 @@
     </row>
     <row r="214" hidden="true">
       <c r="A214" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B214" t="s" s="2">
         <v>190</v>
@@ -27880,7 +27875,7 @@
     </row>
     <row r="215" hidden="true">
       <c r="A215" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B215" t="s" s="2">
         <v>194</v>
@@ -27906,17 +27901,15 @@
         <v>79</v>
       </c>
       <c r="K215" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="L215" t="s" s="2">
         <v>317</v>
       </c>
       <c r="M215" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="N215" t="s" s="2">
-        <v>279</v>
-      </c>
+        <v>318</v>
+      </c>
+      <c r="N215" s="2"/>
       <c r="O215" s="2"/>
       <c r="P215" t="s" s="2">
         <v>79</v>
@@ -27980,16 +27973,16 @@
         <v>79</v>
       </c>
       <c r="AK215" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AL215" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM215" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AN215" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AO215" t="s" s="2">
         <v>79</v>
@@ -28000,7 +27993,7 @@
     </row>
     <row r="216" hidden="true">
       <c r="A216" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B216" t="s" s="2">
         <v>198</v>
@@ -28118,7 +28111,7 @@
     </row>
     <row r="217" hidden="true">
       <c r="A217" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B217" t="s" s="2">
         <v>202</v>
@@ -28236,7 +28229,7 @@
     </row>
     <row r="218" hidden="true">
       <c r="A218" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B218" t="s" s="2">
         <v>203</v>
@@ -28356,7 +28349,7 @@
     </row>
     <row r="219" hidden="true">
       <c r="A219" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B219" t="s" s="2">
         <v>204</v>
@@ -28478,7 +28471,7 @@
     </row>
     <row r="220" hidden="true">
       <c r="A220" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B220" t="s" s="2">
         <v>205</v>
@@ -28598,7 +28591,7 @@
     </row>
     <row r="221" hidden="true">
       <c r="A221" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B221" t="s" s="2">
         <v>211</v>
@@ -28718,7 +28711,7 @@
     </row>
     <row r="222" hidden="true">
       <c r="A222" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B222" t="s" s="2">
         <v>216</v>
@@ -28836,7 +28829,7 @@
     </row>
     <row r="223" hidden="true">
       <c r="A223" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B223" t="s" s="2">
         <v>220</v>
@@ -28954,7 +28947,7 @@
     </row>
     <row r="224" hidden="true">
       <c r="A224" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B224" t="s" s="2">
         <v>221</v>
@@ -29074,7 +29067,7 @@
     </row>
     <row r="225" hidden="true">
       <c r="A225" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B225" t="s" s="2">
         <v>222</v>
@@ -29196,7 +29189,7 @@
     </row>
     <row r="226" hidden="true">
       <c r="A226" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B226" t="s" s="2">
         <v>223</v>
@@ -29314,7 +29307,7 @@
     </row>
     <row r="227" hidden="true">
       <c r="A227" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B227" t="s" s="2">
         <v>228</v>
@@ -29434,7 +29427,7 @@
     </row>
     <row r="228" hidden="true">
       <c r="A228" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B228" t="s" s="2">
         <v>232</v>
@@ -29552,7 +29545,7 @@
     </row>
     <row r="229" hidden="true">
       <c r="A229" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B229" t="s" s="2">
         <v>235</v>
@@ -29670,7 +29663,7 @@
     </row>
     <row r="230" hidden="true">
       <c r="A230" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B230" t="s" s="2">
         <v>237</v>
@@ -29788,7 +29781,7 @@
     </row>
     <row r="231" hidden="true">
       <c r="A231" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B231" t="s" s="2">
         <v>240</v>
@@ -29906,7 +29899,7 @@
     </row>
     <row r="232" hidden="true">
       <c r="A232" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B232" t="s" s="2">
         <v>243</v>
@@ -30024,7 +30017,7 @@
     </row>
     <row r="233" hidden="true">
       <c r="A233" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B233" t="s" s="2">
         <v>247</v>
@@ -30142,7 +30135,7 @@
     </row>
     <row r="234" hidden="true">
       <c r="A234" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B234" t="s" s="2">
         <v>248</v>
@@ -30262,7 +30255,7 @@
     </row>
     <row r="235" hidden="true">
       <c r="A235" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B235" t="s" s="2">
         <v>249</v>
@@ -30384,7 +30377,7 @@
     </row>
     <row r="236" hidden="true">
       <c r="A236" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B236" t="s" s="2">
         <v>250</v>
@@ -30502,7 +30495,7 @@
     </row>
     <row r="237" hidden="true">
       <c r="A237" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B237" t="s" s="2">
         <v>253</v>
@@ -30620,7 +30613,7 @@
     </row>
     <row r="238" hidden="true">
       <c r="A238" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B238" t="s" s="2">
         <v>256</v>
@@ -30740,7 +30733,7 @@
     </row>
     <row r="239" hidden="true">
       <c r="A239" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B239" t="s" s="2">
         <v>260</v>
@@ -30860,7 +30853,7 @@
     </row>
     <row r="240" hidden="true">
       <c r="A240" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B240" t="s" s="2">
         <v>264</v>
@@ -30980,13 +30973,13 @@
     </row>
     <row r="241" hidden="true">
       <c r="A241" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B241" t="s" s="2">
         <v>178</v>
       </c>
       <c r="C241" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="D241" t="s" s="2">
         <v>79</v>
@@ -31100,7 +31093,7 @@
     </row>
     <row r="242" hidden="true">
       <c r="A242" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B242" t="s" s="2">
         <v>184</v>
@@ -31218,7 +31211,7 @@
     </row>
     <row r="243" hidden="true">
       <c r="A243" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B243" t="s" s="2">
         <v>185</v>
@@ -31338,7 +31331,7 @@
     </row>
     <row r="244" hidden="true">
       <c r="A244" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B244" t="s" s="2">
         <v>186</v>
@@ -31460,7 +31453,7 @@
     </row>
     <row r="245" hidden="true">
       <c r="A245" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B245" t="s" s="2">
         <v>187</v>
@@ -31578,7 +31571,7 @@
     </row>
     <row r="246" hidden="true">
       <c r="A246" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B246" t="s" s="2">
         <v>190</v>
@@ -31698,7 +31691,7 @@
     </row>
     <row r="247" hidden="true">
       <c r="A247" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B247" t="s" s="2">
         <v>194</v>
@@ -31724,17 +31717,15 @@
         <v>79</v>
       </c>
       <c r="K247" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="L247" t="s" s="2">
         <v>317</v>
       </c>
       <c r="M247" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="N247" t="s" s="2">
-        <v>279</v>
-      </c>
+        <v>318</v>
+      </c>
+      <c r="N247" s="2"/>
       <c r="O247" s="2"/>
       <c r="P247" t="s" s="2">
         <v>79</v>
@@ -31798,16 +31789,16 @@
         <v>79</v>
       </c>
       <c r="AK247" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AL247" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM247" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AN247" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AO247" t="s" s="2">
         <v>79</v>
@@ -31818,7 +31809,7 @@
     </row>
     <row r="248" hidden="true">
       <c r="A248" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B248" t="s" s="2">
         <v>198</v>
@@ -31936,7 +31927,7 @@
     </row>
     <row r="249" hidden="true">
       <c r="A249" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B249" t="s" s="2">
         <v>202</v>
@@ -32054,7 +32045,7 @@
     </row>
     <row r="250" hidden="true">
       <c r="A250" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B250" t="s" s="2">
         <v>203</v>
@@ -32174,7 +32165,7 @@
     </row>
     <row r="251" hidden="true">
       <c r="A251" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B251" t="s" s="2">
         <v>204</v>
@@ -32296,7 +32287,7 @@
     </row>
     <row r="252" hidden="true">
       <c r="A252" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B252" t="s" s="2">
         <v>205</v>
@@ -32416,7 +32407,7 @@
     </row>
     <row r="253" hidden="true">
       <c r="A253" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B253" t="s" s="2">
         <v>211</v>
@@ -32536,7 +32527,7 @@
     </row>
     <row r="254" hidden="true">
       <c r="A254" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B254" t="s" s="2">
         <v>216</v>
@@ -32654,7 +32645,7 @@
     </row>
     <row r="255" hidden="true">
       <c r="A255" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B255" t="s" s="2">
         <v>220</v>
@@ -32772,7 +32763,7 @@
     </row>
     <row r="256" hidden="true">
       <c r="A256" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B256" t="s" s="2">
         <v>221</v>
@@ -32892,7 +32883,7 @@
     </row>
     <row r="257" hidden="true">
       <c r="A257" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B257" t="s" s="2">
         <v>222</v>
@@ -33014,7 +33005,7 @@
     </row>
     <row r="258" hidden="true">
       <c r="A258" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B258" t="s" s="2">
         <v>223</v>
@@ -33132,7 +33123,7 @@
     </row>
     <row r="259" hidden="true">
       <c r="A259" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B259" t="s" s="2">
         <v>228</v>
@@ -33252,7 +33243,7 @@
     </row>
     <row r="260" hidden="true">
       <c r="A260" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B260" t="s" s="2">
         <v>232</v>
@@ -33370,7 +33361,7 @@
     </row>
     <row r="261" hidden="true">
       <c r="A261" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B261" t="s" s="2">
         <v>235</v>
@@ -33488,7 +33479,7 @@
     </row>
     <row r="262" hidden="true">
       <c r="A262" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B262" t="s" s="2">
         <v>237</v>
@@ -33606,7 +33597,7 @@
     </row>
     <row r="263" hidden="true">
       <c r="A263" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B263" t="s" s="2">
         <v>240</v>
@@ -33724,7 +33715,7 @@
     </row>
     <row r="264" hidden="true">
       <c r="A264" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B264" t="s" s="2">
         <v>243</v>
@@ -33842,7 +33833,7 @@
     </row>
     <row r="265" hidden="true">
       <c r="A265" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B265" t="s" s="2">
         <v>247</v>
@@ -33960,7 +33951,7 @@
     </row>
     <row r="266" hidden="true">
       <c r="A266" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B266" t="s" s="2">
         <v>248</v>
@@ -34080,7 +34071,7 @@
     </row>
     <row r="267" hidden="true">
       <c r="A267" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B267" t="s" s="2">
         <v>249</v>
@@ -34202,7 +34193,7 @@
     </row>
     <row r="268" hidden="true">
       <c r="A268" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B268" t="s" s="2">
         <v>250</v>
@@ -34320,7 +34311,7 @@
     </row>
     <row r="269" hidden="true">
       <c r="A269" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B269" t="s" s="2">
         <v>253</v>
@@ -34438,7 +34429,7 @@
     </row>
     <row r="270" hidden="true">
       <c r="A270" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B270" t="s" s="2">
         <v>256</v>
@@ -34558,7 +34549,7 @@
     </row>
     <row r="271" hidden="true">
       <c r="A271" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B271" t="s" s="2">
         <v>260</v>
@@ -34678,7 +34669,7 @@
     </row>
     <row r="272" hidden="true">
       <c r="A272" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B272" t="s" s="2">
         <v>264</v>
@@ -34798,13 +34789,13 @@
     </row>
     <row r="273" hidden="true">
       <c r="A273" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B273" t="s" s="2">
         <v>178</v>
       </c>
       <c r="C273" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="D273" t="s" s="2">
         <v>79</v>
@@ -34918,7 +34909,7 @@
     </row>
     <row r="274" hidden="true">
       <c r="A274" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B274" t="s" s="2">
         <v>184</v>
@@ -35036,7 +35027,7 @@
     </row>
     <row r="275" hidden="true">
       <c r="A275" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B275" t="s" s="2">
         <v>185</v>
@@ -35156,7 +35147,7 @@
     </row>
     <row r="276" hidden="true">
       <c r="A276" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B276" t="s" s="2">
         <v>186</v>
@@ -35278,7 +35269,7 @@
     </row>
     <row r="277" hidden="true">
       <c r="A277" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B277" t="s" s="2">
         <v>187</v>
@@ -35396,7 +35387,7 @@
     </row>
     <row r="278" hidden="true">
       <c r="A278" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B278" t="s" s="2">
         <v>190</v>
@@ -35516,7 +35507,7 @@
     </row>
     <row r="279" hidden="true">
       <c r="A279" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B279" t="s" s="2">
         <v>194</v>
@@ -35542,17 +35533,15 @@
         <v>79</v>
       </c>
       <c r="K279" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="L279" t="s" s="2">
         <v>317</v>
       </c>
       <c r="M279" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="N279" t="s" s="2">
-        <v>279</v>
-      </c>
+        <v>318</v>
+      </c>
+      <c r="N279" s="2"/>
       <c r="O279" s="2"/>
       <c r="P279" t="s" s="2">
         <v>79</v>
@@ -35616,16 +35605,16 @@
         <v>79</v>
       </c>
       <c r="AK279" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AL279" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM279" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AN279" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AO279" t="s" s="2">
         <v>79</v>
@@ -35636,7 +35625,7 @@
     </row>
     <row r="280" hidden="true">
       <c r="A280" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B280" t="s" s="2">
         <v>198</v>
@@ -35754,7 +35743,7 @@
     </row>
     <row r="281" hidden="true">
       <c r="A281" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B281" t="s" s="2">
         <v>202</v>
@@ -35872,7 +35861,7 @@
     </row>
     <row r="282" hidden="true">
       <c r="A282" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B282" t="s" s="2">
         <v>203</v>
@@ -35992,7 +35981,7 @@
     </row>
     <row r="283" hidden="true">
       <c r="A283" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B283" t="s" s="2">
         <v>204</v>
@@ -36114,7 +36103,7 @@
     </row>
     <row r="284" hidden="true">
       <c r="A284" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B284" t="s" s="2">
         <v>205</v>
@@ -36234,7 +36223,7 @@
     </row>
     <row r="285" hidden="true">
       <c r="A285" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B285" t="s" s="2">
         <v>211</v>
@@ -36354,7 +36343,7 @@
     </row>
     <row r="286" hidden="true">
       <c r="A286" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B286" t="s" s="2">
         <v>216</v>
@@ -36472,7 +36461,7 @@
     </row>
     <row r="287" hidden="true">
       <c r="A287" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B287" t="s" s="2">
         <v>220</v>
@@ -36590,7 +36579,7 @@
     </row>
     <row r="288" hidden="true">
       <c r="A288" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B288" t="s" s="2">
         <v>221</v>
@@ -36710,7 +36699,7 @@
     </row>
     <row r="289" hidden="true">
       <c r="A289" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B289" t="s" s="2">
         <v>222</v>
@@ -36832,7 +36821,7 @@
     </row>
     <row r="290" hidden="true">
       <c r="A290" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B290" t="s" s="2">
         <v>223</v>
@@ -36950,7 +36939,7 @@
     </row>
     <row r="291" hidden="true">
       <c r="A291" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B291" t="s" s="2">
         <v>228</v>
@@ -37070,7 +37059,7 @@
     </row>
     <row r="292" hidden="true">
       <c r="A292" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B292" t="s" s="2">
         <v>232</v>
@@ -37188,7 +37177,7 @@
     </row>
     <row r="293" hidden="true">
       <c r="A293" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B293" t="s" s="2">
         <v>235</v>
@@ -37306,7 +37295,7 @@
     </row>
     <row r="294" hidden="true">
       <c r="A294" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B294" t="s" s="2">
         <v>237</v>
@@ -37424,7 +37413,7 @@
     </row>
     <row r="295" hidden="true">
       <c r="A295" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B295" t="s" s="2">
         <v>240</v>
@@ -37542,7 +37531,7 @@
     </row>
     <row r="296" hidden="true">
       <c r="A296" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B296" t="s" s="2">
         <v>243</v>
@@ -37660,7 +37649,7 @@
     </row>
     <row r="297" hidden="true">
       <c r="A297" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B297" t="s" s="2">
         <v>247</v>
@@ -37778,7 +37767,7 @@
     </row>
     <row r="298" hidden="true">
       <c r="A298" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B298" t="s" s="2">
         <v>248</v>
@@ -37898,7 +37887,7 @@
     </row>
     <row r="299" hidden="true">
       <c r="A299" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B299" t="s" s="2">
         <v>249</v>
@@ -38020,7 +38009,7 @@
     </row>
     <row r="300" hidden="true">
       <c r="A300" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B300" t="s" s="2">
         <v>250</v>
@@ -38138,7 +38127,7 @@
     </row>
     <row r="301" hidden="true">
       <c r="A301" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B301" t="s" s="2">
         <v>253</v>
@@ -38256,7 +38245,7 @@
     </row>
     <row r="302" hidden="true">
       <c r="A302" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="B302" t="s" s="2">
         <v>256</v>
@@ -38376,7 +38365,7 @@
     </row>
     <row r="303" hidden="true">
       <c r="A303" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B303" t="s" s="2">
         <v>260</v>
@@ -38496,7 +38485,7 @@
     </row>
     <row r="304" hidden="true">
       <c r="A304" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B304" t="s" s="2">
         <v>264</v>
@@ -38616,13 +38605,13 @@
     </row>
     <row r="305" hidden="true">
       <c r="A305" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B305" t="s" s="2">
         <v>178</v>
       </c>
       <c r="C305" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="D305" t="s" s="2">
         <v>79</v>
@@ -38736,7 +38725,7 @@
     </row>
     <row r="306" hidden="true">
       <c r="A306" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B306" t="s" s="2">
         <v>184</v>
@@ -38854,7 +38843,7 @@
     </row>
     <row r="307" hidden="true">
       <c r="A307" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B307" t="s" s="2">
         <v>185</v>
@@ -38974,7 +38963,7 @@
     </row>
     <row r="308" hidden="true">
       <c r="A308" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="B308" t="s" s="2">
         <v>186</v>
@@ -39096,7 +39085,7 @@
     </row>
     <row r="309" hidden="true">
       <c r="A309" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B309" t="s" s="2">
         <v>187</v>
@@ -39214,7 +39203,7 @@
     </row>
     <row r="310" hidden="true">
       <c r="A310" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B310" t="s" s="2">
         <v>190</v>
@@ -39334,7 +39323,7 @@
     </row>
     <row r="311" hidden="true">
       <c r="A311" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B311" t="s" s="2">
         <v>194</v>
@@ -39360,17 +39349,15 @@
         <v>79</v>
       </c>
       <c r="K311" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="L311" t="s" s="2">
         <v>317</v>
       </c>
       <c r="M311" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="N311" t="s" s="2">
-        <v>279</v>
-      </c>
+        <v>318</v>
+      </c>
+      <c r="N311" s="2"/>
       <c r="O311" s="2"/>
       <c r="P311" t="s" s="2">
         <v>79</v>
@@ -39434,16 +39421,16 @@
         <v>79</v>
       </c>
       <c r="AK311" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="AL311" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM311" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AN311" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AO311" t="s" s="2">
         <v>79</v>
@@ -39454,7 +39441,7 @@
     </row>
     <row r="312" hidden="true">
       <c r="A312" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B312" t="s" s="2">
         <v>198</v>
@@ -39572,7 +39559,7 @@
     </row>
     <row r="313" hidden="true">
       <c r="A313" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B313" t="s" s="2">
         <v>202</v>
@@ -39690,7 +39677,7 @@
     </row>
     <row r="314" hidden="true">
       <c r="A314" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B314" t="s" s="2">
         <v>203</v>
@@ -39810,7 +39797,7 @@
     </row>
     <row r="315" hidden="true">
       <c r="A315" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B315" t="s" s="2">
         <v>204</v>
@@ -39932,7 +39919,7 @@
     </row>
     <row r="316" hidden="true">
       <c r="A316" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B316" t="s" s="2">
         <v>205</v>
@@ -40052,7 +40039,7 @@
     </row>
     <row r="317" hidden="true">
       <c r="A317" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B317" t="s" s="2">
         <v>211</v>
@@ -40172,7 +40159,7 @@
     </row>
     <row r="318" hidden="true">
       <c r="A318" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B318" t="s" s="2">
         <v>216</v>
@@ -40290,7 +40277,7 @@
     </row>
     <row r="319" hidden="true">
       <c r="A319" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B319" t="s" s="2">
         <v>220</v>
@@ -40408,7 +40395,7 @@
     </row>
     <row r="320" hidden="true">
       <c r="A320" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B320" t="s" s="2">
         <v>221</v>
@@ -40528,7 +40515,7 @@
     </row>
     <row r="321" hidden="true">
       <c r="A321" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B321" t="s" s="2">
         <v>222</v>
@@ -40650,7 +40637,7 @@
     </row>
     <row r="322" hidden="true">
       <c r="A322" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B322" t="s" s="2">
         <v>223</v>
@@ -40768,7 +40755,7 @@
     </row>
     <row r="323" hidden="true">
       <c r="A323" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B323" t="s" s="2">
         <v>228</v>
@@ -40888,7 +40875,7 @@
     </row>
     <row r="324" hidden="true">
       <c r="A324" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B324" t="s" s="2">
         <v>232</v>
@@ -41006,7 +40993,7 @@
     </row>
     <row r="325" hidden="true">
       <c r="A325" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="B325" t="s" s="2">
         <v>235</v>
@@ -41124,7 +41111,7 @@
     </row>
     <row r="326" hidden="true">
       <c r="A326" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B326" t="s" s="2">
         <v>237</v>
@@ -41242,7 +41229,7 @@
     </row>
     <row r="327" hidden="true">
       <c r="A327" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="B327" t="s" s="2">
         <v>240</v>
@@ -41360,7 +41347,7 @@
     </row>
     <row r="328" hidden="true">
       <c r="A328" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B328" t="s" s="2">
         <v>243</v>
@@ -41478,7 +41465,7 @@
     </row>
     <row r="329" hidden="true">
       <c r="A329" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B329" t="s" s="2">
         <v>247</v>
@@ -41596,7 +41583,7 @@
     </row>
     <row r="330" hidden="true">
       <c r="A330" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B330" t="s" s="2">
         <v>248</v>
@@ -41716,7 +41703,7 @@
     </row>
     <row r="331" hidden="true">
       <c r="A331" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B331" t="s" s="2">
         <v>249</v>
@@ -41838,7 +41825,7 @@
     </row>
     <row r="332" hidden="true">
       <c r="A332" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B332" t="s" s="2">
         <v>250</v>
@@ -41956,7 +41943,7 @@
     </row>
     <row r="333" hidden="true">
       <c r="A333" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B333" t="s" s="2">
         <v>253</v>
@@ -42074,7 +42061,7 @@
     </row>
     <row r="334" hidden="true">
       <c r="A334" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B334" t="s" s="2">
         <v>256</v>
@@ -42194,7 +42181,7 @@
     </row>
     <row r="335" hidden="true">
       <c r="A335" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B335" t="s" s="2">
         <v>260</v>
@@ -42314,7 +42301,7 @@
     </row>
     <row r="336" hidden="true">
       <c r="A336" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="B336" t="s" s="2">
         <v>264</v>
@@ -42434,13 +42421,13 @@
     </row>
     <row r="337" hidden="true">
       <c r="A337" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="B337" t="s" s="2">
         <v>178</v>
       </c>
       <c r="C337" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="D337" t="s" s="2">
         <v>79</v>
@@ -42554,7 +42541,7 @@
     </row>
     <row r="338" hidden="true">
       <c r="A338" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B338" t="s" s="2">
         <v>184</v>
@@ -42672,7 +42659,7 @@
     </row>
     <row r="339" hidden="true">
       <c r="A339" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="B339" t="s" s="2">
         <v>185</v>
@@ -42792,7 +42779,7 @@
     </row>
     <row r="340" hidden="true">
       <c r="A340" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="B340" t="s" s="2">
         <v>186</v>
@@ -42914,7 +42901,7 @@
     </row>
     <row r="341" hidden="true">
       <c r="A341" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B341" t="s" s="2">
         <v>187</v>
@@ -43032,7 +43019,7 @@
     </row>
     <row r="342" hidden="true">
       <c r="A342" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="B342" t="s" s="2">
         <v>190</v>
@@ -43152,14 +43139,14 @@
     </row>
     <row r="343" hidden="true">
       <c r="A343" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B343" t="s" s="2">
         <v>194</v>
       </c>
       <c r="C343" s="2"/>
       <c r="D343" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="E343" s="2"/>
       <c r="F343" t="s" s="2">
@@ -43178,13 +43165,13 @@
         <v>79</v>
       </c>
       <c r="K343" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="L343" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="M343" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="N343" s="2"/>
       <c r="O343" s="2"/>
@@ -43250,7 +43237,7 @@
         <v>79</v>
       </c>
       <c r="AK343" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="AL343" t="s" s="2">
         <v>79</v>
@@ -43259,7 +43246,7 @@
         <v>79</v>
       </c>
       <c r="AN343" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="AO343" t="s" s="2">
         <v>79</v>
@@ -43270,7 +43257,7 @@
     </row>
     <row r="344" hidden="true">
       <c r="A344" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="B344" t="s" s="2">
         <v>198</v>
@@ -43388,7 +43375,7 @@
     </row>
     <row r="345" hidden="true">
       <c r="A345" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="B345" t="s" s="2">
         <v>202</v>
@@ -43506,7 +43493,7 @@
     </row>
     <row r="346" hidden="true">
       <c r="A346" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="B346" t="s" s="2">
         <v>203</v>
@@ -43626,7 +43613,7 @@
     </row>
     <row r="347" hidden="true">
       <c r="A347" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="B347" t="s" s="2">
         <v>204</v>
@@ -43748,7 +43735,7 @@
     </row>
     <row r="348" hidden="true">
       <c r="A348" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B348" t="s" s="2">
         <v>205</v>
@@ -43868,7 +43855,7 @@
     </row>
     <row r="349" hidden="true">
       <c r="A349" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="B349" t="s" s="2">
         <v>211</v>
@@ -43988,7 +43975,7 @@
     </row>
     <row r="350" hidden="true">
       <c r="A350" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="B350" t="s" s="2">
         <v>216</v>
@@ -44106,7 +44093,7 @@
     </row>
     <row r="351" hidden="true">
       <c r="A351" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="B351" t="s" s="2">
         <v>220</v>
@@ -44224,7 +44211,7 @@
     </row>
     <row r="352" hidden="true">
       <c r="A352" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="B352" t="s" s="2">
         <v>221</v>
@@ -44344,7 +44331,7 @@
     </row>
     <row r="353" hidden="true">
       <c r="A353" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="B353" t="s" s="2">
         <v>222</v>
@@ -44466,7 +44453,7 @@
     </row>
     <row r="354" hidden="true">
       <c r="A354" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="B354" t="s" s="2">
         <v>223</v>
@@ -44584,7 +44571,7 @@
     </row>
     <row r="355" hidden="true">
       <c r="A355" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="B355" t="s" s="2">
         <v>228</v>
@@ -44704,7 +44691,7 @@
     </row>
     <row r="356" hidden="true">
       <c r="A356" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="B356" t="s" s="2">
         <v>232</v>
@@ -44822,7 +44809,7 @@
     </row>
     <row r="357" hidden="true">
       <c r="A357" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="B357" t="s" s="2">
         <v>235</v>
@@ -44940,7 +44927,7 @@
     </row>
     <row r="358" hidden="true">
       <c r="A358" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="B358" t="s" s="2">
         <v>237</v>
@@ -45058,7 +45045,7 @@
     </row>
     <row r="359" hidden="true">
       <c r="A359" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="B359" t="s" s="2">
         <v>240</v>
@@ -45176,7 +45163,7 @@
     </row>
     <row r="360" hidden="true">
       <c r="A360" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="B360" t="s" s="2">
         <v>243</v>
@@ -45294,7 +45281,7 @@
     </row>
     <row r="361" hidden="true">
       <c r="A361" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="B361" t="s" s="2">
         <v>247</v>
@@ -45412,7 +45399,7 @@
     </row>
     <row r="362" hidden="true">
       <c r="A362" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="B362" t="s" s="2">
         <v>248</v>
@@ -45532,7 +45519,7 @@
     </row>
     <row r="363" hidden="true">
       <c r="A363" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="B363" t="s" s="2">
         <v>249</v>
@@ -45654,7 +45641,7 @@
     </row>
     <row r="364" hidden="true">
       <c r="A364" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="B364" t="s" s="2">
         <v>250</v>
@@ -45772,7 +45759,7 @@
     </row>
     <row r="365" hidden="true">
       <c r="A365" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B365" t="s" s="2">
         <v>253</v>
@@ -45890,7 +45877,7 @@
     </row>
     <row r="366" hidden="true">
       <c r="A366" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="B366" t="s" s="2">
         <v>256</v>
@@ -46010,7 +45997,7 @@
     </row>
     <row r="367" hidden="true">
       <c r="A367" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="B367" t="s" s="2">
         <v>260</v>
@@ -46130,7 +46117,7 @@
     </row>
     <row r="368" hidden="true">
       <c r="A368" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="B368" t="s" s="2">
         <v>264</v>
@@ -46250,10 +46237,10 @@
     </row>
     <row r="369" hidden="true">
       <c r="A369" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="B369" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="C369" s="2"/>
       <c r="D369" t="s" s="2">
@@ -46276,19 +46263,19 @@
         <v>90</v>
       </c>
       <c r="K369" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="L369" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="M369" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="N369" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="O369" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="P369" t="s" s="2">
         <v>79</v>
@@ -46337,7 +46324,7 @@
         <v>79</v>
       </c>
       <c r="AF369" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="AG369" t="s" s="2">
         <v>80</v>

--- a/docs/StructureDefinition-VAERSBundle.xlsx
+++ b/docs/StructureDefinition-VAERSBundle.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13927" uniqueCount="637">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13935" uniqueCount="636">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.345</t>
+    <t>0.65.348</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-26T15:27:18+00:00</t>
+    <t>2024-09-15T08:33:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1012,9 +1012,6 @@
   </si>
   <si>
     <t>Immunization event information</t>
-  </si>
-  <si>
-    <t>Describes the event of a patient being administered a vaccine or a record of an immunization as reported by a patient, a clinician or another party.</t>
   </si>
   <si>
     <t>1963: reference</t>
@@ -12643,9 +12640,11 @@
         <v>317</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="N87" s="2"/>
+        <v>279</v>
+      </c>
+      <c r="N87" t="s" s="2">
+        <v>279</v>
+      </c>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
         <v>79</v>
@@ -12709,16 +12708,16 @@
         <v>79</v>
       </c>
       <c r="AK87" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="AL87" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM87" t="s" s="2">
         <v>319</v>
       </c>
-      <c r="AL87" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM87" t="s" s="2">
+      <c r="AN87" t="s" s="2">
         <v>320</v>
-      </c>
-      <c r="AN87" t="s" s="2">
-        <v>321</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>79</v>
@@ -12729,7 +12728,7 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B88" t="s" s="2">
         <v>198</v>
@@ -12847,7 +12846,7 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B89" t="s" s="2">
         <v>202</v>
@@ -12965,7 +12964,7 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B90" t="s" s="2">
         <v>203</v>
@@ -13085,7 +13084,7 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B91" t="s" s="2">
         <v>204</v>
@@ -13207,7 +13206,7 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B92" t="s" s="2">
         <v>205</v>
@@ -13327,7 +13326,7 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B93" t="s" s="2">
         <v>211</v>
@@ -13447,7 +13446,7 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B94" t="s" s="2">
         <v>216</v>
@@ -13565,7 +13564,7 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B95" t="s" s="2">
         <v>220</v>
@@ -13683,7 +13682,7 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B96" t="s" s="2">
         <v>221</v>
@@ -13803,7 +13802,7 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B97" t="s" s="2">
         <v>222</v>
@@ -13925,7 +13924,7 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B98" t="s" s="2">
         <v>223</v>
@@ -14043,7 +14042,7 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B99" t="s" s="2">
         <v>228</v>
@@ -14163,7 +14162,7 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B100" t="s" s="2">
         <v>232</v>
@@ -14281,7 +14280,7 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B101" t="s" s="2">
         <v>235</v>
@@ -14399,7 +14398,7 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B102" t="s" s="2">
         <v>237</v>
@@ -14517,7 +14516,7 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B103" t="s" s="2">
         <v>240</v>
@@ -14635,7 +14634,7 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B104" t="s" s="2">
         <v>243</v>
@@ -14753,7 +14752,7 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B105" t="s" s="2">
         <v>247</v>
@@ -14871,7 +14870,7 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B106" t="s" s="2">
         <v>248</v>
@@ -14991,7 +14990,7 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B107" t="s" s="2">
         <v>249</v>
@@ -15113,7 +15112,7 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B108" t="s" s="2">
         <v>250</v>
@@ -15231,7 +15230,7 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B109" t="s" s="2">
         <v>253</v>
@@ -15349,7 +15348,7 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B110" t="s" s="2">
         <v>256</v>
@@ -15469,7 +15468,7 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B111" t="s" s="2">
         <v>260</v>
@@ -15589,7 +15588,7 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B112" t="s" s="2">
         <v>264</v>
@@ -15709,13 +15708,13 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B113" t="s" s="2">
         <v>178</v>
       </c>
       <c r="C113" t="s" s="2">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="D113" t="s" s="2">
         <v>79</v>
@@ -15829,7 +15828,7 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B114" t="s" s="2">
         <v>184</v>
@@ -15947,7 +15946,7 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B115" t="s" s="2">
         <v>185</v>
@@ -16067,7 +16066,7 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B116" t="s" s="2">
         <v>186</v>
@@ -16189,7 +16188,7 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B117" t="s" s="2">
         <v>187</v>
@@ -16307,7 +16306,7 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B118" t="s" s="2">
         <v>190</v>
@@ -16427,7 +16426,7 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B119" t="s" s="2">
         <v>194</v>
@@ -16453,15 +16452,17 @@
         <v>79</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="L119" t="s" s="2">
         <v>317</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="N119" s="2"/>
+        <v>279</v>
+      </c>
+      <c r="N119" t="s" s="2">
+        <v>279</v>
+      </c>
       <c r="O119" s="2"/>
       <c r="P119" t="s" s="2">
         <v>79</v>
@@ -16525,16 +16526,16 @@
         <v>79</v>
       </c>
       <c r="AK119" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="AL119" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM119" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="AN119" t="s" s="2">
         <v>320</v>
-      </c>
-      <c r="AN119" t="s" s="2">
-        <v>321</v>
       </c>
       <c r="AO119" t="s" s="2">
         <v>79</v>
@@ -16545,7 +16546,7 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B120" t="s" s="2">
         <v>198</v>
@@ -16663,7 +16664,7 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B121" t="s" s="2">
         <v>202</v>
@@ -16781,7 +16782,7 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B122" t="s" s="2">
         <v>203</v>
@@ -16901,7 +16902,7 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B123" t="s" s="2">
         <v>204</v>
@@ -17023,7 +17024,7 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B124" t="s" s="2">
         <v>205</v>
@@ -17143,7 +17144,7 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B125" t="s" s="2">
         <v>211</v>
@@ -17263,7 +17264,7 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B126" t="s" s="2">
         <v>216</v>
@@ -17381,7 +17382,7 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B127" t="s" s="2">
         <v>220</v>
@@ -17499,7 +17500,7 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B128" t="s" s="2">
         <v>221</v>
@@ -17619,7 +17620,7 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B129" t="s" s="2">
         <v>222</v>
@@ -17741,7 +17742,7 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B130" t="s" s="2">
         <v>223</v>
@@ -17859,7 +17860,7 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B131" t="s" s="2">
         <v>228</v>
@@ -17979,7 +17980,7 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B132" t="s" s="2">
         <v>232</v>
@@ -18097,7 +18098,7 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B133" t="s" s="2">
         <v>235</v>
@@ -18215,7 +18216,7 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B134" t="s" s="2">
         <v>237</v>
@@ -18333,7 +18334,7 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B135" t="s" s="2">
         <v>240</v>
@@ -18451,7 +18452,7 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B136" t="s" s="2">
         <v>243</v>
@@ -18569,7 +18570,7 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B137" t="s" s="2">
         <v>247</v>
@@ -18687,7 +18688,7 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B138" t="s" s="2">
         <v>248</v>
@@ -18807,7 +18808,7 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B139" t="s" s="2">
         <v>249</v>
@@ -18929,7 +18930,7 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B140" t="s" s="2">
         <v>250</v>
@@ -19047,7 +19048,7 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B141" t="s" s="2">
         <v>253</v>
@@ -19165,7 +19166,7 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B142" t="s" s="2">
         <v>256</v>
@@ -19285,7 +19286,7 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B143" t="s" s="2">
         <v>260</v>
@@ -19405,7 +19406,7 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B144" t="s" s="2">
         <v>264</v>
@@ -19525,13 +19526,13 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B145" t="s" s="2">
         <v>178</v>
       </c>
       <c r="C145" t="s" s="2">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="D145" t="s" s="2">
         <v>79</v>
@@ -19645,7 +19646,7 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B146" t="s" s="2">
         <v>184</v>
@@ -19763,7 +19764,7 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B147" t="s" s="2">
         <v>185</v>
@@ -19883,7 +19884,7 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B148" t="s" s="2">
         <v>186</v>
@@ -20005,7 +20006,7 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B149" t="s" s="2">
         <v>187</v>
@@ -20123,7 +20124,7 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B150" t="s" s="2">
         <v>190</v>
@@ -20243,7 +20244,7 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B151" t="s" s="2">
         <v>194</v>
@@ -20269,15 +20270,17 @@
         <v>79</v>
       </c>
       <c r="K151" t="s" s="2">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="L151" t="s" s="2">
         <v>317</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="N151" s="2"/>
+        <v>279</v>
+      </c>
+      <c r="N151" t="s" s="2">
+        <v>279</v>
+      </c>
       <c r="O151" s="2"/>
       <c r="P151" t="s" s="2">
         <v>79</v>
@@ -20341,16 +20344,16 @@
         <v>79</v>
       </c>
       <c r="AK151" t="s" s="2">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="AL151" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM151" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="AN151" t="s" s="2">
         <v>320</v>
-      </c>
-      <c r="AN151" t="s" s="2">
-        <v>321</v>
       </c>
       <c r="AO151" t="s" s="2">
         <v>79</v>
@@ -20361,7 +20364,7 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B152" t="s" s="2">
         <v>198</v>
@@ -20479,7 +20482,7 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B153" t="s" s="2">
         <v>202</v>
@@ -20597,7 +20600,7 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B154" t="s" s="2">
         <v>203</v>
@@ -20717,7 +20720,7 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B155" t="s" s="2">
         <v>204</v>
@@ -20839,7 +20842,7 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B156" t="s" s="2">
         <v>205</v>
@@ -20959,7 +20962,7 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B157" t="s" s="2">
         <v>211</v>
@@ -21079,7 +21082,7 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B158" t="s" s="2">
         <v>216</v>
@@ -21197,7 +21200,7 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B159" t="s" s="2">
         <v>220</v>
@@ -21315,7 +21318,7 @@
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B160" t="s" s="2">
         <v>221</v>
@@ -21435,7 +21438,7 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B161" t="s" s="2">
         <v>222</v>
@@ -21557,7 +21560,7 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B162" t="s" s="2">
         <v>223</v>
@@ -21675,7 +21678,7 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B163" t="s" s="2">
         <v>228</v>
@@ -21795,7 +21798,7 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B164" t="s" s="2">
         <v>232</v>
@@ -21913,7 +21916,7 @@
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B165" t="s" s="2">
         <v>235</v>
@@ -22031,7 +22034,7 @@
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B166" t="s" s="2">
         <v>237</v>
@@ -22149,7 +22152,7 @@
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B167" t="s" s="2">
         <v>240</v>
@@ -22267,7 +22270,7 @@
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B168" t="s" s="2">
         <v>243</v>
@@ -22385,7 +22388,7 @@
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B169" t="s" s="2">
         <v>247</v>
@@ -22503,7 +22506,7 @@
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B170" t="s" s="2">
         <v>248</v>
@@ -22623,7 +22626,7 @@
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B171" t="s" s="2">
         <v>249</v>
@@ -22745,7 +22748,7 @@
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B172" t="s" s="2">
         <v>250</v>
@@ -22863,7 +22866,7 @@
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B173" t="s" s="2">
         <v>253</v>
@@ -22981,7 +22984,7 @@
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B174" t="s" s="2">
         <v>256</v>
@@ -23101,7 +23104,7 @@
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B175" t="s" s="2">
         <v>260</v>
@@ -23221,7 +23224,7 @@
     </row>
     <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B176" t="s" s="2">
         <v>264</v>
@@ -23341,13 +23344,13 @@
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B177" t="s" s="2">
         <v>178</v>
       </c>
       <c r="C177" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="D177" t="s" s="2">
         <v>79</v>
@@ -23461,7 +23464,7 @@
     </row>
     <row r="178" hidden="true">
       <c r="A178" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B178" t="s" s="2">
         <v>184</v>
@@ -23579,7 +23582,7 @@
     </row>
     <row r="179" hidden="true">
       <c r="A179" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B179" t="s" s="2">
         <v>185</v>
@@ -23699,7 +23702,7 @@
     </row>
     <row r="180" hidden="true">
       <c r="A180" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B180" t="s" s="2">
         <v>186</v>
@@ -23821,7 +23824,7 @@
     </row>
     <row r="181" hidden="true">
       <c r="A181" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B181" t="s" s="2">
         <v>187</v>
@@ -23939,7 +23942,7 @@
     </row>
     <row r="182" hidden="true">
       <c r="A182" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B182" t="s" s="2">
         <v>190</v>
@@ -24059,7 +24062,7 @@
     </row>
     <row r="183" hidden="true">
       <c r="A183" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B183" t="s" s="2">
         <v>194</v>
@@ -24085,15 +24088,17 @@
         <v>79</v>
       </c>
       <c r="K183" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="L183" t="s" s="2">
         <v>317</v>
       </c>
       <c r="M183" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="N183" s="2"/>
+        <v>279</v>
+      </c>
+      <c r="N183" t="s" s="2">
+        <v>279</v>
+      </c>
       <c r="O183" s="2"/>
       <c r="P183" t="s" s="2">
         <v>79</v>
@@ -24157,16 +24162,16 @@
         <v>79</v>
       </c>
       <c r="AK183" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="AL183" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM183" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="AN183" t="s" s="2">
         <v>320</v>
-      </c>
-      <c r="AN183" t="s" s="2">
-        <v>321</v>
       </c>
       <c r="AO183" t="s" s="2">
         <v>79</v>
@@ -24177,7 +24182,7 @@
     </row>
     <row r="184" hidden="true">
       <c r="A184" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B184" t="s" s="2">
         <v>198</v>
@@ -24295,7 +24300,7 @@
     </row>
     <row r="185" hidden="true">
       <c r="A185" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="B185" t="s" s="2">
         <v>202</v>
@@ -24413,7 +24418,7 @@
     </row>
     <row r="186" hidden="true">
       <c r="A186" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B186" t="s" s="2">
         <v>203</v>
@@ -24533,7 +24538,7 @@
     </row>
     <row r="187" hidden="true">
       <c r="A187" t="s" s="2">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B187" t="s" s="2">
         <v>204</v>
@@ -24655,7 +24660,7 @@
     </row>
     <row r="188" hidden="true">
       <c r="A188" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B188" t="s" s="2">
         <v>205</v>
@@ -24775,7 +24780,7 @@
     </row>
     <row r="189" hidden="true">
       <c r="A189" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B189" t="s" s="2">
         <v>211</v>
@@ -24895,7 +24900,7 @@
     </row>
     <row r="190" hidden="true">
       <c r="A190" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B190" t="s" s="2">
         <v>216</v>
@@ -25013,7 +25018,7 @@
     </row>
     <row r="191" hidden="true">
       <c r="A191" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B191" t="s" s="2">
         <v>220</v>
@@ -25131,7 +25136,7 @@
     </row>
     <row r="192" hidden="true">
       <c r="A192" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B192" t="s" s="2">
         <v>221</v>
@@ -25251,7 +25256,7 @@
     </row>
     <row r="193" hidden="true">
       <c r="A193" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B193" t="s" s="2">
         <v>222</v>
@@ -25373,7 +25378,7 @@
     </row>
     <row r="194" hidden="true">
       <c r="A194" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B194" t="s" s="2">
         <v>223</v>
@@ -25491,7 +25496,7 @@
     </row>
     <row r="195" hidden="true">
       <c r="A195" t="s" s="2">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B195" t="s" s="2">
         <v>228</v>
@@ -25611,7 +25616,7 @@
     </row>
     <row r="196" hidden="true">
       <c r="A196" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B196" t="s" s="2">
         <v>232</v>
@@ -25729,7 +25734,7 @@
     </row>
     <row r="197" hidden="true">
       <c r="A197" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B197" t="s" s="2">
         <v>235</v>
@@ -25847,7 +25852,7 @@
     </row>
     <row r="198" hidden="true">
       <c r="A198" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B198" t="s" s="2">
         <v>237</v>
@@ -25965,7 +25970,7 @@
     </row>
     <row r="199" hidden="true">
       <c r="A199" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B199" t="s" s="2">
         <v>240</v>
@@ -26083,7 +26088,7 @@
     </row>
     <row r="200" hidden="true">
       <c r="A200" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B200" t="s" s="2">
         <v>243</v>
@@ -26201,7 +26206,7 @@
     </row>
     <row r="201" hidden="true">
       <c r="A201" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="B201" t="s" s="2">
         <v>247</v>
@@ -26319,7 +26324,7 @@
     </row>
     <row r="202" hidden="true">
       <c r="A202" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="B202" t="s" s="2">
         <v>248</v>
@@ -26439,7 +26444,7 @@
     </row>
     <row r="203" hidden="true">
       <c r="A203" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B203" t="s" s="2">
         <v>249</v>
@@ -26561,7 +26566,7 @@
     </row>
     <row r="204" hidden="true">
       <c r="A204" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B204" t="s" s="2">
         <v>250</v>
@@ -26679,7 +26684,7 @@
     </row>
     <row r="205" hidden="true">
       <c r="A205" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B205" t="s" s="2">
         <v>253</v>
@@ -26797,7 +26802,7 @@
     </row>
     <row r="206" hidden="true">
       <c r="A206" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="B206" t="s" s="2">
         <v>256</v>
@@ -26917,7 +26922,7 @@
     </row>
     <row r="207" hidden="true">
       <c r="A207" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B207" t="s" s="2">
         <v>260</v>
@@ -27037,7 +27042,7 @@
     </row>
     <row r="208" hidden="true">
       <c r="A208" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B208" t="s" s="2">
         <v>264</v>
@@ -27157,13 +27162,13 @@
     </row>
     <row r="209" hidden="true">
       <c r="A209" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B209" t="s" s="2">
         <v>178</v>
       </c>
       <c r="C209" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="D209" t="s" s="2">
         <v>79</v>
@@ -27277,7 +27282,7 @@
     </row>
     <row r="210" hidden="true">
       <c r="A210" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="B210" t="s" s="2">
         <v>184</v>
@@ -27395,7 +27400,7 @@
     </row>
     <row r="211" hidden="true">
       <c r="A211" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B211" t="s" s="2">
         <v>185</v>
@@ -27515,7 +27520,7 @@
     </row>
     <row r="212" hidden="true">
       <c r="A212" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B212" t="s" s="2">
         <v>186</v>
@@ -27637,7 +27642,7 @@
     </row>
     <row r="213" hidden="true">
       <c r="A213" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B213" t="s" s="2">
         <v>187</v>
@@ -27755,7 +27760,7 @@
     </row>
     <row r="214" hidden="true">
       <c r="A214" t="s" s="2">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="B214" t="s" s="2">
         <v>190</v>
@@ -27875,7 +27880,7 @@
     </row>
     <row r="215" hidden="true">
       <c r="A215" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B215" t="s" s="2">
         <v>194</v>
@@ -27901,15 +27906,17 @@
         <v>79</v>
       </c>
       <c r="K215" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="L215" t="s" s="2">
         <v>317</v>
       </c>
       <c r="M215" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="N215" s="2"/>
+        <v>279</v>
+      </c>
+      <c r="N215" t="s" s="2">
+        <v>279</v>
+      </c>
       <c r="O215" s="2"/>
       <c r="P215" t="s" s="2">
         <v>79</v>
@@ -27973,16 +27980,16 @@
         <v>79</v>
       </c>
       <c r="AK215" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="AL215" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM215" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="AN215" t="s" s="2">
         <v>320</v>
-      </c>
-      <c r="AN215" t="s" s="2">
-        <v>321</v>
       </c>
       <c r="AO215" t="s" s="2">
         <v>79</v>
@@ -27993,7 +28000,7 @@
     </row>
     <row r="216" hidden="true">
       <c r="A216" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B216" t="s" s="2">
         <v>198</v>
@@ -28111,7 +28118,7 @@
     </row>
     <row r="217" hidden="true">
       <c r="A217" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B217" t="s" s="2">
         <v>202</v>
@@ -28229,7 +28236,7 @@
     </row>
     <row r="218" hidden="true">
       <c r="A218" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B218" t="s" s="2">
         <v>203</v>
@@ -28349,7 +28356,7 @@
     </row>
     <row r="219" hidden="true">
       <c r="A219" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="B219" t="s" s="2">
         <v>204</v>
@@ -28471,7 +28478,7 @@
     </row>
     <row r="220" hidden="true">
       <c r="A220" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B220" t="s" s="2">
         <v>205</v>
@@ -28591,7 +28598,7 @@
     </row>
     <row r="221" hidden="true">
       <c r="A221" t="s" s="2">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B221" t="s" s="2">
         <v>211</v>
@@ -28711,7 +28718,7 @@
     </row>
     <row r="222" hidden="true">
       <c r="A222" t="s" s="2">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="B222" t="s" s="2">
         <v>216</v>
@@ -28829,7 +28836,7 @@
     </row>
     <row r="223" hidden="true">
       <c r="A223" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B223" t="s" s="2">
         <v>220</v>
@@ -28947,7 +28954,7 @@
     </row>
     <row r="224" hidden="true">
       <c r="A224" t="s" s="2">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B224" t="s" s="2">
         <v>221</v>
@@ -29067,7 +29074,7 @@
     </row>
     <row r="225" hidden="true">
       <c r="A225" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B225" t="s" s="2">
         <v>222</v>
@@ -29189,7 +29196,7 @@
     </row>
     <row r="226" hidden="true">
       <c r="A226" t="s" s="2">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B226" t="s" s="2">
         <v>223</v>
@@ -29307,7 +29314,7 @@
     </row>
     <row r="227" hidden="true">
       <c r="A227" t="s" s="2">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="B227" t="s" s="2">
         <v>228</v>
@@ -29427,7 +29434,7 @@
     </row>
     <row r="228" hidden="true">
       <c r="A228" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B228" t="s" s="2">
         <v>232</v>
@@ -29545,7 +29552,7 @@
     </row>
     <row r="229" hidden="true">
       <c r="A229" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B229" t="s" s="2">
         <v>235</v>
@@ -29663,7 +29670,7 @@
     </row>
     <row r="230" hidden="true">
       <c r="A230" t="s" s="2">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B230" t="s" s="2">
         <v>237</v>
@@ -29781,7 +29788,7 @@
     </row>
     <row r="231" hidden="true">
       <c r="A231" t="s" s="2">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B231" t="s" s="2">
         <v>240</v>
@@ -29899,7 +29906,7 @@
     </row>
     <row r="232" hidden="true">
       <c r="A232" t="s" s="2">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B232" t="s" s="2">
         <v>243</v>
@@ -30017,7 +30024,7 @@
     </row>
     <row r="233" hidden="true">
       <c r="A233" t="s" s="2">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B233" t="s" s="2">
         <v>247</v>
@@ -30135,7 +30142,7 @@
     </row>
     <row r="234" hidden="true">
       <c r="A234" t="s" s="2">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B234" t="s" s="2">
         <v>248</v>
@@ -30255,7 +30262,7 @@
     </row>
     <row r="235" hidden="true">
       <c r="A235" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B235" t="s" s="2">
         <v>249</v>
@@ -30377,7 +30384,7 @@
     </row>
     <row r="236" hidden="true">
       <c r="A236" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B236" t="s" s="2">
         <v>250</v>
@@ -30495,7 +30502,7 @@
     </row>
     <row r="237" hidden="true">
       <c r="A237" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B237" t="s" s="2">
         <v>253</v>
@@ -30613,7 +30620,7 @@
     </row>
     <row r="238" hidden="true">
       <c r="A238" t="s" s="2">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B238" t="s" s="2">
         <v>256</v>
@@ -30733,7 +30740,7 @@
     </row>
     <row r="239" hidden="true">
       <c r="A239" t="s" s="2">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B239" t="s" s="2">
         <v>260</v>
@@ -30853,7 +30860,7 @@
     </row>
     <row r="240" hidden="true">
       <c r="A240" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="B240" t="s" s="2">
         <v>264</v>
@@ -30973,13 +30980,13 @@
     </row>
     <row r="241" hidden="true">
       <c r="A241" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B241" t="s" s="2">
         <v>178</v>
       </c>
       <c r="C241" t="s" s="2">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="D241" t="s" s="2">
         <v>79</v>
@@ -31093,7 +31100,7 @@
     </row>
     <row r="242" hidden="true">
       <c r="A242" t="s" s="2">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="B242" t="s" s="2">
         <v>184</v>
@@ -31211,7 +31218,7 @@
     </row>
     <row r="243" hidden="true">
       <c r="A243" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="B243" t="s" s="2">
         <v>185</v>
@@ -31331,7 +31338,7 @@
     </row>
     <row r="244" hidden="true">
       <c r="A244" t="s" s="2">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="B244" t="s" s="2">
         <v>186</v>
@@ -31453,7 +31460,7 @@
     </row>
     <row r="245" hidden="true">
       <c r="A245" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B245" t="s" s="2">
         <v>187</v>
@@ -31571,7 +31578,7 @@
     </row>
     <row r="246" hidden="true">
       <c r="A246" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="B246" t="s" s="2">
         <v>190</v>
@@ -31691,7 +31698,7 @@
     </row>
     <row r="247" hidden="true">
       <c r="A247" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B247" t="s" s="2">
         <v>194</v>
@@ -31717,15 +31724,17 @@
         <v>79</v>
       </c>
       <c r="K247" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="L247" t="s" s="2">
         <v>317</v>
       </c>
       <c r="M247" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="N247" s="2"/>
+        <v>279</v>
+      </c>
+      <c r="N247" t="s" s="2">
+        <v>279</v>
+      </c>
       <c r="O247" s="2"/>
       <c r="P247" t="s" s="2">
         <v>79</v>
@@ -31789,16 +31798,16 @@
         <v>79</v>
       </c>
       <c r="AK247" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="AL247" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM247" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="AN247" t="s" s="2">
         <v>320</v>
-      </c>
-      <c r="AN247" t="s" s="2">
-        <v>321</v>
       </c>
       <c r="AO247" t="s" s="2">
         <v>79</v>
@@ -31809,7 +31818,7 @@
     </row>
     <row r="248" hidden="true">
       <c r="A248" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B248" t="s" s="2">
         <v>198</v>
@@ -31927,7 +31936,7 @@
     </row>
     <row r="249" hidden="true">
       <c r="A249" t="s" s="2">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B249" t="s" s="2">
         <v>202</v>
@@ -32045,7 +32054,7 @@
     </row>
     <row r="250" hidden="true">
       <c r="A250" t="s" s="2">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B250" t="s" s="2">
         <v>203</v>
@@ -32165,7 +32174,7 @@
     </row>
     <row r="251" hidden="true">
       <c r="A251" t="s" s="2">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="B251" t="s" s="2">
         <v>204</v>
@@ -32287,7 +32296,7 @@
     </row>
     <row r="252" hidden="true">
       <c r="A252" t="s" s="2">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="B252" t="s" s="2">
         <v>205</v>
@@ -32407,7 +32416,7 @@
     </row>
     <row r="253" hidden="true">
       <c r="A253" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="B253" t="s" s="2">
         <v>211</v>
@@ -32527,7 +32536,7 @@
     </row>
     <row r="254" hidden="true">
       <c r="A254" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B254" t="s" s="2">
         <v>216</v>
@@ -32645,7 +32654,7 @@
     </row>
     <row r="255" hidden="true">
       <c r="A255" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="B255" t="s" s="2">
         <v>220</v>
@@ -32763,7 +32772,7 @@
     </row>
     <row r="256" hidden="true">
       <c r="A256" t="s" s="2">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B256" t="s" s="2">
         <v>221</v>
@@ -32883,7 +32892,7 @@
     </row>
     <row r="257" hidden="true">
       <c r="A257" t="s" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="B257" t="s" s="2">
         <v>222</v>
@@ -33005,7 +33014,7 @@
     </row>
     <row r="258" hidden="true">
       <c r="A258" t="s" s="2">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="B258" t="s" s="2">
         <v>223</v>
@@ -33123,7 +33132,7 @@
     </row>
     <row r="259" hidden="true">
       <c r="A259" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B259" t="s" s="2">
         <v>228</v>
@@ -33243,7 +33252,7 @@
     </row>
     <row r="260" hidden="true">
       <c r="A260" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B260" t="s" s="2">
         <v>232</v>
@@ -33361,7 +33370,7 @@
     </row>
     <row r="261" hidden="true">
       <c r="A261" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="B261" t="s" s="2">
         <v>235</v>
@@ -33479,7 +33488,7 @@
     </row>
     <row r="262" hidden="true">
       <c r="A262" t="s" s="2">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="B262" t="s" s="2">
         <v>237</v>
@@ -33597,7 +33606,7 @@
     </row>
     <row r="263" hidden="true">
       <c r="A263" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B263" t="s" s="2">
         <v>240</v>
@@ -33715,7 +33724,7 @@
     </row>
     <row r="264" hidden="true">
       <c r="A264" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B264" t="s" s="2">
         <v>243</v>
@@ -33833,7 +33842,7 @@
     </row>
     <row r="265" hidden="true">
       <c r="A265" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B265" t="s" s="2">
         <v>247</v>
@@ -33951,7 +33960,7 @@
     </row>
     <row r="266" hidden="true">
       <c r="A266" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="B266" t="s" s="2">
         <v>248</v>
@@ -34071,7 +34080,7 @@
     </row>
     <row r="267" hidden="true">
       <c r="A267" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B267" t="s" s="2">
         <v>249</v>
@@ -34193,7 +34202,7 @@
     </row>
     <row r="268" hidden="true">
       <c r="A268" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B268" t="s" s="2">
         <v>250</v>
@@ -34311,7 +34320,7 @@
     </row>
     <row r="269" hidden="true">
       <c r="A269" t="s" s="2">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="B269" t="s" s="2">
         <v>253</v>
@@ -34429,7 +34438,7 @@
     </row>
     <row r="270" hidden="true">
       <c r="A270" t="s" s="2">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="B270" t="s" s="2">
         <v>256</v>
@@ -34549,7 +34558,7 @@
     </row>
     <row r="271" hidden="true">
       <c r="A271" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="B271" t="s" s="2">
         <v>260</v>
@@ -34669,7 +34678,7 @@
     </row>
     <row r="272" hidden="true">
       <c r="A272" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B272" t="s" s="2">
         <v>264</v>
@@ -34789,13 +34798,13 @@
     </row>
     <row r="273" hidden="true">
       <c r="A273" t="s" s="2">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="B273" t="s" s="2">
         <v>178</v>
       </c>
       <c r="C273" t="s" s="2">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="D273" t="s" s="2">
         <v>79</v>
@@ -34909,7 +34918,7 @@
     </row>
     <row r="274" hidden="true">
       <c r="A274" t="s" s="2">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B274" t="s" s="2">
         <v>184</v>
@@ -35027,7 +35036,7 @@
     </row>
     <row r="275" hidden="true">
       <c r="A275" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B275" t="s" s="2">
         <v>185</v>
@@ -35147,7 +35156,7 @@
     </row>
     <row r="276" hidden="true">
       <c r="A276" t="s" s="2">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="B276" t="s" s="2">
         <v>186</v>
@@ -35269,7 +35278,7 @@
     </row>
     <row r="277" hidden="true">
       <c r="A277" t="s" s="2">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="B277" t="s" s="2">
         <v>187</v>
@@ -35387,7 +35396,7 @@
     </row>
     <row r="278" hidden="true">
       <c r="A278" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B278" t="s" s="2">
         <v>190</v>
@@ -35507,7 +35516,7 @@
     </row>
     <row r="279" hidden="true">
       <c r="A279" t="s" s="2">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="B279" t="s" s="2">
         <v>194</v>
@@ -35533,15 +35542,17 @@
         <v>79</v>
       </c>
       <c r="K279" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="L279" t="s" s="2">
         <v>317</v>
       </c>
       <c r="M279" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="N279" s="2"/>
+        <v>279</v>
+      </c>
+      <c r="N279" t="s" s="2">
+        <v>279</v>
+      </c>
       <c r="O279" s="2"/>
       <c r="P279" t="s" s="2">
         <v>79</v>
@@ -35605,16 +35616,16 @@
         <v>79</v>
       </c>
       <c r="AK279" t="s" s="2">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="AL279" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM279" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="AN279" t="s" s="2">
         <v>320</v>
-      </c>
-      <c r="AN279" t="s" s="2">
-        <v>321</v>
       </c>
       <c r="AO279" t="s" s="2">
         <v>79</v>
@@ -35625,7 +35636,7 @@
     </row>
     <row r="280" hidden="true">
       <c r="A280" t="s" s="2">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B280" t="s" s="2">
         <v>198</v>
@@ -35743,7 +35754,7 @@
     </row>
     <row r="281" hidden="true">
       <c r="A281" t="s" s="2">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="B281" t="s" s="2">
         <v>202</v>
@@ -35861,7 +35872,7 @@
     </row>
     <row r="282" hidden="true">
       <c r="A282" t="s" s="2">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B282" t="s" s="2">
         <v>203</v>
@@ -35981,7 +35992,7 @@
     </row>
     <row r="283" hidden="true">
       <c r="A283" t="s" s="2">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B283" t="s" s="2">
         <v>204</v>
@@ -36103,7 +36114,7 @@
     </row>
     <row r="284" hidden="true">
       <c r="A284" t="s" s="2">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="B284" t="s" s="2">
         <v>205</v>
@@ -36223,7 +36234,7 @@
     </row>
     <row r="285" hidden="true">
       <c r="A285" t="s" s="2">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="B285" t="s" s="2">
         <v>211</v>
@@ -36343,7 +36354,7 @@
     </row>
     <row r="286" hidden="true">
       <c r="A286" t="s" s="2">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="B286" t="s" s="2">
         <v>216</v>
@@ -36461,7 +36472,7 @@
     </row>
     <row r="287" hidden="true">
       <c r="A287" t="s" s="2">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="B287" t="s" s="2">
         <v>220</v>
@@ -36579,7 +36590,7 @@
     </row>
     <row r="288" hidden="true">
       <c r="A288" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="B288" t="s" s="2">
         <v>221</v>
@@ -36699,7 +36710,7 @@
     </row>
     <row r="289" hidden="true">
       <c r="A289" t="s" s="2">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="B289" t="s" s="2">
         <v>222</v>
@@ -36821,7 +36832,7 @@
     </row>
     <row r="290" hidden="true">
       <c r="A290" t="s" s="2">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="B290" t="s" s="2">
         <v>223</v>
@@ -36939,7 +36950,7 @@
     </row>
     <row r="291" hidden="true">
       <c r="A291" t="s" s="2">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="B291" t="s" s="2">
         <v>228</v>
@@ -37059,7 +37070,7 @@
     </row>
     <row r="292" hidden="true">
       <c r="A292" t="s" s="2">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B292" t="s" s="2">
         <v>232</v>
@@ -37177,7 +37188,7 @@
     </row>
     <row r="293" hidden="true">
       <c r="A293" t="s" s="2">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B293" t="s" s="2">
         <v>235</v>
@@ -37295,7 +37306,7 @@
     </row>
     <row r="294" hidden="true">
       <c r="A294" t="s" s="2">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B294" t="s" s="2">
         <v>237</v>
@@ -37413,7 +37424,7 @@
     </row>
     <row r="295" hidden="true">
       <c r="A295" t="s" s="2">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B295" t="s" s="2">
         <v>240</v>
@@ -37531,7 +37542,7 @@
     </row>
     <row r="296" hidden="true">
       <c r="A296" t="s" s="2">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B296" t="s" s="2">
         <v>243</v>
@@ -37649,7 +37660,7 @@
     </row>
     <row r="297" hidden="true">
       <c r="A297" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B297" t="s" s="2">
         <v>247</v>
@@ -37767,7 +37778,7 @@
     </row>
     <row r="298" hidden="true">
       <c r="A298" t="s" s="2">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B298" t="s" s="2">
         <v>248</v>
@@ -37887,7 +37898,7 @@
     </row>
     <row r="299" hidden="true">
       <c r="A299" t="s" s="2">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B299" t="s" s="2">
         <v>249</v>
@@ -38009,7 +38020,7 @@
     </row>
     <row r="300" hidden="true">
       <c r="A300" t="s" s="2">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="B300" t="s" s="2">
         <v>250</v>
@@ -38127,7 +38138,7 @@
     </row>
     <row r="301" hidden="true">
       <c r="A301" t="s" s="2">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="B301" t="s" s="2">
         <v>253</v>
@@ -38245,7 +38256,7 @@
     </row>
     <row r="302" hidden="true">
       <c r="A302" t="s" s="2">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="B302" t="s" s="2">
         <v>256</v>
@@ -38365,7 +38376,7 @@
     </row>
     <row r="303" hidden="true">
       <c r="A303" t="s" s="2">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B303" t="s" s="2">
         <v>260</v>
@@ -38485,7 +38496,7 @@
     </row>
     <row r="304" hidden="true">
       <c r="A304" t="s" s="2">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B304" t="s" s="2">
         <v>264</v>
@@ -38605,13 +38616,13 @@
     </row>
     <row r="305" hidden="true">
       <c r="A305" t="s" s="2">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="B305" t="s" s="2">
         <v>178</v>
       </c>
       <c r="C305" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="D305" t="s" s="2">
         <v>79</v>
@@ -38725,7 +38736,7 @@
     </row>
     <row r="306" hidden="true">
       <c r="A306" t="s" s="2">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B306" t="s" s="2">
         <v>184</v>
@@ -38843,7 +38854,7 @@
     </row>
     <row r="307" hidden="true">
       <c r="A307" t="s" s="2">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B307" t="s" s="2">
         <v>185</v>
@@ -38963,7 +38974,7 @@
     </row>
     <row r="308" hidden="true">
       <c r="A308" t="s" s="2">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="B308" t="s" s="2">
         <v>186</v>
@@ -39085,7 +39096,7 @@
     </row>
     <row r="309" hidden="true">
       <c r="A309" t="s" s="2">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="B309" t="s" s="2">
         <v>187</v>
@@ -39203,7 +39214,7 @@
     </row>
     <row r="310" hidden="true">
       <c r="A310" t="s" s="2">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="B310" t="s" s="2">
         <v>190</v>
@@ -39323,7 +39334,7 @@
     </row>
     <row r="311" hidden="true">
       <c r="A311" t="s" s="2">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="B311" t="s" s="2">
         <v>194</v>
@@ -39349,15 +39360,17 @@
         <v>79</v>
       </c>
       <c r="K311" t="s" s="2">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="L311" t="s" s="2">
         <v>317</v>
       </c>
       <c r="M311" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="N311" s="2"/>
+        <v>279</v>
+      </c>
+      <c r="N311" t="s" s="2">
+        <v>279</v>
+      </c>
       <c r="O311" s="2"/>
       <c r="P311" t="s" s="2">
         <v>79</v>
@@ -39421,16 +39434,16 @@
         <v>79</v>
       </c>
       <c r="AK311" t="s" s="2">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="AL311" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM311" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="AN311" t="s" s="2">
         <v>320</v>
-      </c>
-      <c r="AN311" t="s" s="2">
-        <v>321</v>
       </c>
       <c r="AO311" t="s" s="2">
         <v>79</v>
@@ -39441,7 +39454,7 @@
     </row>
     <row r="312" hidden="true">
       <c r="A312" t="s" s="2">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B312" t="s" s="2">
         <v>198</v>
@@ -39559,7 +39572,7 @@
     </row>
     <row r="313" hidden="true">
       <c r="A313" t="s" s="2">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B313" t="s" s="2">
         <v>202</v>
@@ -39677,7 +39690,7 @@
     </row>
     <row r="314" hidden="true">
       <c r="A314" t="s" s="2">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="B314" t="s" s="2">
         <v>203</v>
@@ -39797,7 +39810,7 @@
     </row>
     <row r="315" hidden="true">
       <c r="A315" t="s" s="2">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="B315" t="s" s="2">
         <v>204</v>
@@ -39919,7 +39932,7 @@
     </row>
     <row r="316" hidden="true">
       <c r="A316" t="s" s="2">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="B316" t="s" s="2">
         <v>205</v>
@@ -40039,7 +40052,7 @@
     </row>
     <row r="317" hidden="true">
       <c r="A317" t="s" s="2">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="B317" t="s" s="2">
         <v>211</v>
@@ -40159,7 +40172,7 @@
     </row>
     <row r="318" hidden="true">
       <c r="A318" t="s" s="2">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="B318" t="s" s="2">
         <v>216</v>
@@ -40277,7 +40290,7 @@
     </row>
     <row r="319" hidden="true">
       <c r="A319" t="s" s="2">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="B319" t="s" s="2">
         <v>220</v>
@@ -40395,7 +40408,7 @@
     </row>
     <row r="320" hidden="true">
       <c r="A320" t="s" s="2">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="B320" t="s" s="2">
         <v>221</v>
@@ -40515,7 +40528,7 @@
     </row>
     <row r="321" hidden="true">
       <c r="A321" t="s" s="2">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="B321" t="s" s="2">
         <v>222</v>
@@ -40637,7 +40650,7 @@
     </row>
     <row r="322" hidden="true">
       <c r="A322" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B322" t="s" s="2">
         <v>223</v>
@@ -40755,7 +40768,7 @@
     </row>
     <row r="323" hidden="true">
       <c r="A323" t="s" s="2">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B323" t="s" s="2">
         <v>228</v>
@@ -40875,7 +40888,7 @@
     </row>
     <row r="324" hidden="true">
       <c r="A324" t="s" s="2">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="B324" t="s" s="2">
         <v>232</v>
@@ -40993,7 +41006,7 @@
     </row>
     <row r="325" hidden="true">
       <c r="A325" t="s" s="2">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="B325" t="s" s="2">
         <v>235</v>
@@ -41111,7 +41124,7 @@
     </row>
     <row r="326" hidden="true">
       <c r="A326" t="s" s="2">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="B326" t="s" s="2">
         <v>237</v>
@@ -41229,7 +41242,7 @@
     </row>
     <row r="327" hidden="true">
       <c r="A327" t="s" s="2">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B327" t="s" s="2">
         <v>240</v>
@@ -41347,7 +41360,7 @@
     </row>
     <row r="328" hidden="true">
       <c r="A328" t="s" s="2">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="B328" t="s" s="2">
         <v>243</v>
@@ -41465,7 +41478,7 @@
     </row>
     <row r="329" hidden="true">
       <c r="A329" t="s" s="2">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B329" t="s" s="2">
         <v>247</v>
@@ -41583,7 +41596,7 @@
     </row>
     <row r="330" hidden="true">
       <c r="A330" t="s" s="2">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B330" t="s" s="2">
         <v>248</v>
@@ -41703,7 +41716,7 @@
     </row>
     <row r="331" hidden="true">
       <c r="A331" t="s" s="2">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="B331" t="s" s="2">
         <v>249</v>
@@ -41825,7 +41838,7 @@
     </row>
     <row r="332" hidden="true">
       <c r="A332" t="s" s="2">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="B332" t="s" s="2">
         <v>250</v>
@@ -41943,7 +41956,7 @@
     </row>
     <row r="333" hidden="true">
       <c r="A333" t="s" s="2">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="B333" t="s" s="2">
         <v>253</v>
@@ -42061,7 +42074,7 @@
     </row>
     <row r="334" hidden="true">
       <c r="A334" t="s" s="2">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="B334" t="s" s="2">
         <v>256</v>
@@ -42181,7 +42194,7 @@
     </row>
     <row r="335" hidden="true">
       <c r="A335" t="s" s="2">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="B335" t="s" s="2">
         <v>260</v>
@@ -42301,7 +42314,7 @@
     </row>
     <row r="336" hidden="true">
       <c r="A336" t="s" s="2">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="B336" t="s" s="2">
         <v>264</v>
@@ -42421,13 +42434,13 @@
     </row>
     <row r="337" hidden="true">
       <c r="A337" t="s" s="2">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B337" t="s" s="2">
         <v>178</v>
       </c>
       <c r="C337" t="s" s="2">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="D337" t="s" s="2">
         <v>79</v>
@@ -42541,7 +42554,7 @@
     </row>
     <row r="338" hidden="true">
       <c r="A338" t="s" s="2">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="B338" t="s" s="2">
         <v>184</v>
@@ -42659,7 +42672,7 @@
     </row>
     <row r="339" hidden="true">
       <c r="A339" t="s" s="2">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="B339" t="s" s="2">
         <v>185</v>
@@ -42779,7 +42792,7 @@
     </row>
     <row r="340" hidden="true">
       <c r="A340" t="s" s="2">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="B340" t="s" s="2">
         <v>186</v>
@@ -42901,7 +42914,7 @@
     </row>
     <row r="341" hidden="true">
       <c r="A341" t="s" s="2">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="B341" t="s" s="2">
         <v>187</v>
@@ -43019,7 +43032,7 @@
     </row>
     <row r="342" hidden="true">
       <c r="A342" t="s" s="2">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B342" t="s" s="2">
         <v>190</v>
@@ -43139,14 +43152,14 @@
     </row>
     <row r="343" hidden="true">
       <c r="A343" t="s" s="2">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="B343" t="s" s="2">
         <v>194</v>
       </c>
       <c r="C343" s="2"/>
       <c r="D343" t="s" s="2">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="E343" s="2"/>
       <c r="F343" t="s" s="2">
@@ -43165,13 +43178,13 @@
         <v>79</v>
       </c>
       <c r="K343" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="L343" t="s" s="2">
         <v>601</v>
       </c>
-      <c r="L343" t="s" s="2">
+      <c r="M343" t="s" s="2">
         <v>602</v>
-      </c>
-      <c r="M343" t="s" s="2">
-        <v>603</v>
       </c>
       <c r="N343" s="2"/>
       <c r="O343" s="2"/>
@@ -43237,16 +43250,16 @@
         <v>79</v>
       </c>
       <c r="AK343" t="s" s="2">
+        <v>603</v>
+      </c>
+      <c r="AL343" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM343" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN343" t="s" s="2">
         <v>604</v>
-      </c>
-      <c r="AL343" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM343" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN343" t="s" s="2">
-        <v>605</v>
       </c>
       <c r="AO343" t="s" s="2">
         <v>79</v>
@@ -43257,7 +43270,7 @@
     </row>
     <row r="344" hidden="true">
       <c r="A344" t="s" s="2">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="B344" t="s" s="2">
         <v>198</v>
@@ -43375,7 +43388,7 @@
     </row>
     <row r="345" hidden="true">
       <c r="A345" t="s" s="2">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B345" t="s" s="2">
         <v>202</v>
@@ -43493,7 +43506,7 @@
     </row>
     <row r="346" hidden="true">
       <c r="A346" t="s" s="2">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="B346" t="s" s="2">
         <v>203</v>
@@ -43613,7 +43626,7 @@
     </row>
     <row r="347" hidden="true">
       <c r="A347" t="s" s="2">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="B347" t="s" s="2">
         <v>204</v>
@@ -43735,7 +43748,7 @@
     </row>
     <row r="348" hidden="true">
       <c r="A348" t="s" s="2">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="B348" t="s" s="2">
         <v>205</v>
@@ -43855,7 +43868,7 @@
     </row>
     <row r="349" hidden="true">
       <c r="A349" t="s" s="2">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="B349" t="s" s="2">
         <v>211</v>
@@ -43975,7 +43988,7 @@
     </row>
     <row r="350" hidden="true">
       <c r="A350" t="s" s="2">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="B350" t="s" s="2">
         <v>216</v>
@@ -44093,7 +44106,7 @@
     </row>
     <row r="351" hidden="true">
       <c r="A351" t="s" s="2">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="B351" t="s" s="2">
         <v>220</v>
@@ -44211,7 +44224,7 @@
     </row>
     <row r="352" hidden="true">
       <c r="A352" t="s" s="2">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="B352" t="s" s="2">
         <v>221</v>
@@ -44331,7 +44344,7 @@
     </row>
     <row r="353" hidden="true">
       <c r="A353" t="s" s="2">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B353" t="s" s="2">
         <v>222</v>
@@ -44453,7 +44466,7 @@
     </row>
     <row r="354" hidden="true">
       <c r="A354" t="s" s="2">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="B354" t="s" s="2">
         <v>223</v>
@@ -44571,7 +44584,7 @@
     </row>
     <row r="355" hidden="true">
       <c r="A355" t="s" s="2">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="B355" t="s" s="2">
         <v>228</v>
@@ -44691,7 +44704,7 @@
     </row>
     <row r="356" hidden="true">
       <c r="A356" t="s" s="2">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="B356" t="s" s="2">
         <v>232</v>
@@ -44809,7 +44822,7 @@
     </row>
     <row r="357" hidden="true">
       <c r="A357" t="s" s="2">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="B357" t="s" s="2">
         <v>235</v>
@@ -44927,7 +44940,7 @@
     </row>
     <row r="358" hidden="true">
       <c r="A358" t="s" s="2">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="B358" t="s" s="2">
         <v>237</v>
@@ -45045,7 +45058,7 @@
     </row>
     <row r="359" hidden="true">
       <c r="A359" t="s" s="2">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="B359" t="s" s="2">
         <v>240</v>
@@ -45163,7 +45176,7 @@
     </row>
     <row r="360" hidden="true">
       <c r="A360" t="s" s="2">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="B360" t="s" s="2">
         <v>243</v>
@@ -45281,7 +45294,7 @@
     </row>
     <row r="361" hidden="true">
       <c r="A361" t="s" s="2">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B361" t="s" s="2">
         <v>247</v>
@@ -45399,7 +45412,7 @@
     </row>
     <row r="362" hidden="true">
       <c r="A362" t="s" s="2">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="B362" t="s" s="2">
         <v>248</v>
@@ -45519,7 +45532,7 @@
     </row>
     <row r="363" hidden="true">
       <c r="A363" t="s" s="2">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B363" t="s" s="2">
         <v>249</v>
@@ -45641,7 +45654,7 @@
     </row>
     <row r="364" hidden="true">
       <c r="A364" t="s" s="2">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="B364" t="s" s="2">
         <v>250</v>
@@ -45759,7 +45772,7 @@
     </row>
     <row r="365" hidden="true">
       <c r="A365" t="s" s="2">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="B365" t="s" s="2">
         <v>253</v>
@@ -45877,7 +45890,7 @@
     </row>
     <row r="366" hidden="true">
       <c r="A366" t="s" s="2">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="B366" t="s" s="2">
         <v>256</v>
@@ -45997,7 +46010,7 @@
     </row>
     <row r="367" hidden="true">
       <c r="A367" t="s" s="2">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="B367" t="s" s="2">
         <v>260</v>
@@ -46117,7 +46130,7 @@
     </row>
     <row r="368" hidden="true">
       <c r="A368" t="s" s="2">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="B368" t="s" s="2">
         <v>264</v>
@@ -46237,10 +46250,10 @@
     </row>
     <row r="369" hidden="true">
       <c r="A369" t="s" s="2">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="B369" t="s" s="2">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="C369" s="2"/>
       <c r="D369" t="s" s="2">
@@ -46263,19 +46276,19 @@
         <v>90</v>
       </c>
       <c r="K369" t="s" s="2">
+        <v>631</v>
+      </c>
+      <c r="L369" t="s" s="2">
         <v>632</v>
       </c>
-      <c r="L369" t="s" s="2">
+      <c r="M369" t="s" s="2">
         <v>633</v>
       </c>
-      <c r="M369" t="s" s="2">
+      <c r="N369" t="s" s="2">
         <v>634</v>
       </c>
-      <c r="N369" t="s" s="2">
+      <c r="O369" t="s" s="2">
         <v>635</v>
-      </c>
-      <c r="O369" t="s" s="2">
-        <v>636</v>
       </c>
       <c r="P369" t="s" s="2">
         <v>79</v>
@@ -46324,7 +46337,7 @@
         <v>79</v>
       </c>
       <c r="AF369" t="s" s="2">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="AG369" t="s" s="2">
         <v>80</v>

--- a/docs/StructureDefinition-VAERSBundle.xlsx
+++ b/docs/StructureDefinition-VAERSBundle.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.348</t>
+    <t>0.66.354</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-15T08:33:43+00:00</t>
+    <t>2024-09-19T08:45:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -628,7 +628,7 @@
 * Results from operations might involve resources that are not identified.</t>
   </si>
   <si>
-    <t>fullUrl might not be [unique in the context of a resource](bundle.html#bundle-unique). Note that since [FHIR resources do not need to be served through the FHIR API](http://hl7.org/fhir/R4/references.html), the fullURL might be a URN or an absolute URL that does not end with the logical id of the resource (Resource.id). However, but if the fullUrl does look like a RESTful server URL (e.g. meets the [regex](http://hl7.org/fhir/R4/references.html#regex), then the 'id' portion of the fullUrl SHALL end with the Resource.id.
+    <t>fullUrl might not be [unique in the context of a resource](http://hl7.org/fhir/R4/bundle.html#bundle-unique). Note that since [FHIR resources do not need to be served through the FHIR API](http://hl7.org/fhir/R4/references.html), the fullURL might be a URN or an absolute URL that does not end with the logical id of the resource (Resource.id). However, but if the fullUrl does look like a RESTful server URL (e.g. meets the [regex](http://hl7.org/fhir/R4/references.html#regex), then the 'id' portion of the fullUrl SHALL end with the Resource.id.
 Note that the fullUrl is not the same as the canonical URL - it's an absolute url for an endpoint serving the resource (these will happen to have the same value on the canonical server for the resource with the canonical URL).</t>
   </si>
   <si>

--- a/docs/StructureDefinition-VAERSBundle.xlsx
+++ b/docs/StructureDefinition-VAERSBundle.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.354</t>
+    <t>0.66.364</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-19T08:45:12+00:00</t>
+    <t>2024-10-02T18:53:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1007,7 +1007,7 @@
     <t>Bundle.entry:va-vac1.resource</t>
   </si>
   <si>
-    <t xml:space="preserve">Immunization {http://va.gov/fhir/StructureDefinition/VAERSImmunization-vac1}
+    <t xml:space="preserve">Immunization {http://va.gov/fhir/StructureDefinition/VAERSImmunizationvac1}
 </t>
   </si>
   <si>
@@ -1122,7 +1122,7 @@
     <t>Bundle.entry:va-vac2.resource</t>
   </si>
   <si>
-    <t xml:space="preserve">Immunization {http://va.gov/fhir/StructureDefinition/VAERSImmunization-vac2}
+    <t xml:space="preserve">Immunization {http://va.gov/fhir/StructureDefinition/VAERSImmunizationvac2}
 </t>
   </si>
   <si>
@@ -1228,7 +1228,7 @@
     <t>Bundle.entry:va-vac3.resource</t>
   </si>
   <si>
-    <t xml:space="preserve">Immunization {http://va.gov/fhir/StructureDefinition/VAERSImmunization-vac3}
+    <t xml:space="preserve">Immunization {http://va.gov/fhir/StructureDefinition/VAERSImmunizationvac3}
 </t>
   </si>
   <si>
@@ -1334,7 +1334,7 @@
     <t>Bundle.entry:va-vac4.resource</t>
   </si>
   <si>
-    <t xml:space="preserve">Immunization {http://va.gov/fhir/StructureDefinition/VAERSImmunization-vac4}
+    <t xml:space="preserve">Immunization {http://va.gov/fhir/StructureDefinition/VAERSImmunizationvac4}
 </t>
   </si>
   <si>
@@ -1440,7 +1440,7 @@
     <t>Bundle.entry:va-pvac1.resource</t>
   </si>
   <si>
-    <t xml:space="preserve">Immunization {http://va.gov/fhir/StructureDefinition/VAERSImmunization-pvac1}
+    <t xml:space="preserve">Immunization {http://va.gov/fhir/StructureDefinition/VAERSImmunizationpvac1}
 </t>
   </si>
   <si>
@@ -1546,7 +1546,7 @@
     <t>Bundle.entry:va-pvac2.resource</t>
   </si>
   <si>
-    <t xml:space="preserve">Immunization {http://va.gov/fhir/StructureDefinition/VAERSImmunization-pvac2}
+    <t xml:space="preserve">Immunization {http://va.gov/fhir/StructureDefinition/VAERSImmunizationpvac2}
 </t>
   </si>
   <si>
@@ -1652,7 +1652,7 @@
     <t>Bundle.entry:va-pvac3.resource</t>
   </si>
   <si>
-    <t xml:space="preserve">Immunization {http://va.gov/fhir/StructureDefinition/VAERSImmunization-pvac3}
+    <t xml:space="preserve">Immunization {http://va.gov/fhir/StructureDefinition/VAERSImmunizationpvac3}
 </t>
   </si>
   <si>
@@ -1758,7 +1758,7 @@
     <t>Bundle.entry:va-pvac4.resource</t>
   </si>
   <si>
-    <t xml:space="preserve">Immunization {http://va.gov/fhir/StructureDefinition/VAERSImmunization-pvac4}
+    <t xml:space="preserve">Immunization {http://va.gov/fhir/StructureDefinition/VAERSImmunizationpvac4}
 </t>
   </si>
   <si>
@@ -2305,7 +2305,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="75.5078125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="74.84375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-VAERSBundle.xlsx
+++ b/docs/StructureDefinition-VAERSBundle.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.364</t>
+    <t>0.66.366</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-02T18:53:29+00:00</t>
+    <t>2024-10-11T07:57:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSBundle.xlsx
+++ b/docs/StructureDefinition-VAERSBundle.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.366</t>
+    <t>0.66.367</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-11T07:57:28+00:00</t>
+    <t>2024-10-13T09:59:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSBundle.xlsx
+++ b/docs/StructureDefinition-VAERSBundle.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.367</t>
+    <t>0.67.369</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-13T09:59:39+00:00</t>
+    <t>2024-10-18T16:05:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSBundle.xlsx
+++ b/docs/StructureDefinition-VAERSBundle.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.369</t>
+    <t>0.67.370</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-18T16:05:33+00:00</t>
+    <t>2024-10-20T09:02:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSBundle.xlsx
+++ b/docs/StructureDefinition-VAERSBundle.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.370</t>
+    <t>0.67.378</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-20T09:02:32+00:00</t>
+    <t>2024-10-30T12:26:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSBundle.xlsx
+++ b/docs/StructureDefinition-VAERSBundle.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.378</t>
+    <t>0.67.381</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-30T12:26:51+00:00</t>
+    <t>2024-11-03T11:50:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSBundle.xlsx
+++ b/docs/StructureDefinition-VAERSBundle.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.381</t>
+    <t>0.68.397</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-03T11:50:46+00:00</t>
+    <t>2024-11-10T10:13:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSBundle.xlsx
+++ b/docs/StructureDefinition-VAERSBundle.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.397</t>
+    <t>0.68.401</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-10T10:13:24+00:00</t>
+    <t>2024-11-13T21:40:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSBundle.xlsx
+++ b/docs/StructureDefinition-VAERSBundle.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.401</t>
+    <t>0.68.419</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-13T21:40:45+00:00</t>
+    <t>2024-11-25T07:50:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSBundle.xlsx
+++ b/docs/StructureDefinition-VAERSBundle.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.419</t>
+    <t>0.68.424</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-25T07:50:24+00:00</t>
+    <t>2024-11-30T14:03:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSBundle.xlsx
+++ b/docs/StructureDefinition-VAERSBundle.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.424</t>
+    <t>0.68.425</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-30T14:03:16+00:00</t>
+    <t>2024-11-30T15:07:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSBundle.xlsx
+++ b/docs/StructureDefinition-VAERSBundle.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.436</t>
+    <t>0.69.437</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-04T11:34:53+00:00</t>
+    <t>2024-12-04T16:25:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSBundle.xlsx
+++ b/docs/StructureDefinition-VAERSBundle.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.437</t>
+    <t>0.69.438</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-04T16:25:11+00:00</t>
+    <t>2024-12-06T17:18:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSBundle.xlsx
+++ b/docs/StructureDefinition-VAERSBundle.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.438</t>
+    <t>0.69.439</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-06T17:18:58+00:00</t>
+    <t>2024-12-07T11:18:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSBundle.xlsx
+++ b/docs/StructureDefinition-VAERSBundle.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.439</t>
+    <t>0.69.440</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-07T11:18:15+00:00</t>
+    <t>2024-12-08T09:28:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSBundle.xlsx
+++ b/docs/StructureDefinition-VAERSBundle.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.440</t>
+    <t>0.69.442</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-08T09:28:43+00:00</t>
+    <t>2024-12-11T20:06:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSBundle.xlsx
+++ b/docs/StructureDefinition-VAERSBundle.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.442</t>
+    <t>0.69.448</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-11T20:06:32+00:00</t>
+    <t>2024-12-21T10:24:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for ADERS to Bundle</t>
+    <t>This StructureDefinition contains the maps for ADERS to Bundle.</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/docs/StructureDefinition-VAERSBundle.xlsx
+++ b/docs/StructureDefinition-VAERSBundle.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.448</t>
+    <t>1.1.467</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-21T10:24:25+00:00</t>
+    <t>2025-01-04T09:38:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -585,7 +585,7 @@
     <t>An entry in a bundle resource - will either contain a resource or information about a resource (transactions and history only).</t>
   </si>
   <si>
-    <t xml:space="preserve">pattern:$this}
+    <t xml:space="preserve">value:$this}
 </t>
   </si>
   <si>

--- a/docs/StructureDefinition-VAERSBundle.xlsx
+++ b/docs/StructureDefinition-VAERSBundle.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.467</t>
+    <t>1.1.468</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-04T09:38:39+00:00</t>
+    <t>2025-01-04T15:04:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSBundle.xlsx
+++ b/docs/StructureDefinition-VAERSBundle.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.468</t>
+    <t>1.1.477</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-04T15:04:27+00:00</t>
+    <t>2025-01-07T16:27:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSBundle.xlsx
+++ b/docs/StructureDefinition-VAERSBundle.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.477</t>
+    <t>1.1.478</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-07T16:27:08+00:00</t>
+    <t>2025-01-13T09:39:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSBundle.xlsx
+++ b/docs/StructureDefinition-VAERSBundle.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.478</t>
+    <t>1.1.487</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-13T09:39:57+00:00</t>
+    <t>2025-01-17T12:09:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSBundle.xlsx
+++ b/docs/StructureDefinition-VAERSBundle.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.487</t>
+    <t>1.1.491</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T12:09:20+00:00</t>
+    <t>2025-01-17T13:37:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSBundle.xlsx
+++ b/docs/StructureDefinition-VAERSBundle.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.491</t>
+    <t>1.1.494</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T13:37:46+00:00</t>
+    <t>2025-01-25T09:28:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSBundle.xlsx
+++ b/docs/StructureDefinition-VAERSBundle.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.494</t>
+    <t>1.1.500</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-25T09:28:03+00:00</t>
+    <t>2025-02-01T09:13:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSBundle.xlsx
+++ b/docs/StructureDefinition-VAERSBundle.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.500</t>
+    <t>1.2.512</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-01T09:13:38+00:00</t>
+    <t>2025-02-05T16:47:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSBundle.xlsx
+++ b/docs/StructureDefinition-VAERSBundle.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T16:47:13+00:00</t>
+    <t>2025-02-05T17:20:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSBundle.xlsx
+++ b/docs/StructureDefinition-VAERSBundle.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.512</t>
+    <t>1.2.520</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T17:20:26+00:00</t>
+    <t>2025-02-08T12:00:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSBundle.xlsx
+++ b/docs/StructureDefinition-VAERSBundle.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.520</t>
+    <t>1.2.529</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-08T12:00:09+00:00</t>
+    <t>2025-02-20T14:56:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSBundle.xlsx
+++ b/docs/StructureDefinition-VAERSBundle.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.529</t>
+    <t>1.2.531</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:56:35+00:00</t>
+    <t>2025-02-22T09:54:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSBundle.xlsx
+++ b/docs/StructureDefinition-VAERSBundle.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.531</t>
+    <t>1.2.537</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-22T09:54:59+00:00</t>
+    <t>2025-02-24T13:20:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSBundle.xlsx
+++ b/docs/StructureDefinition-VAERSBundle.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T13:20:37+00:00</t>
+    <t>2025-02-25T20:49:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSBundle.xlsx
+++ b/docs/StructureDefinition-VAERSBundle.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.537</t>
+    <t>1.2.540</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-25T20:49:13+00:00</t>
+    <t>2025-03-11T10:08:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSBundle.xlsx
+++ b/docs/StructureDefinition-VAERSBundle.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.540</t>
+    <t>1.3.557</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-11T10:08:33+00:00</t>
+    <t>2025-03-15T09:48:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSBundle.xlsx
+++ b/docs/StructureDefinition-VAERSBundle.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.557</t>
+    <t>1.3.574</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-15T09:48:09+00:00</t>
+    <t>2025-03-22T10:33:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSBundle.xlsx
+++ b/docs/StructureDefinition-VAERSBundle.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.574</t>
+    <t>1.3.575</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-22T10:33:38+00:00</t>
+    <t>2025-03-22T10:56:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSBundle.xlsx
+++ b/docs/StructureDefinition-VAERSBundle.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.575</t>
+    <t>1.3.578</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-22T10:56:07+00:00</t>
+    <t>2025-03-23T10:22:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSBundle.xlsx
+++ b/docs/StructureDefinition-VAERSBundle.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.578</t>
+    <t>1.3.580</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-23T10:22:17+00:00</t>
+    <t>2025-03-23T13:19:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSBundle.xlsx
+++ b/docs/StructureDefinition-VAERSBundle.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.580</t>
+    <t>1.4.588</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-23T13:19:29+00:00</t>
+    <t>2025-04-01T14:43:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
